--- a/output/Data and Chart Outputs/europe_tso_gas_demand_extra_daily.xlsx
+++ b/output/Data and Chart Outputs/europe_tso_gas_demand_extra_daily.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Units" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Chart" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Daily" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Monthly" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -155,7 +156,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Gas consumption: Poland, Romania, Finland (TSO data) (to Sep/26)</a:t>
+              <a:t>Gas consumption: Poland, Romania, Finland, Spain (operator data) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -273,6 +274,42 @@
           </val>
           <smooth val="0"/>
         </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Chart'!E1</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22225">
+              <a:solidFill>
+                <a:srgbClr val="EDA100"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Chart'!$A$2:$A$70</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Chart'!$E$2:$E$70</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
@@ -359,7 +396,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>5</col>
+      <col>6</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -671,7 +708,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A12"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -687,7 +724,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Europe - national gas consumption from the gas TSOs' / market-area operators' own series</t>
+          <t>Europe - national gas consumption from further gas operators' own series (raw operator data, no Eurostat gap-filling)</t>
         </is>
       </c>
     </row>
@@ -702,7 +739,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Germany: Trading Hub Europe aggregated consumption (https://www.tradinghub.eu). France: ODRE open data of GRTgaz, Teréga and RTE (https://odre.opendatasoft.com). Spain: Enagás GTS demand history (https://www.enagas.es/en/technical-management-system/energy-data/demand/history/). Denmark: Energinet Energi Data Service, dataset Gasflow (https://www.energidataservice.dk). Portugal: REN DataHub (https://datahub.ren.pt). Free, no key.</t>
+          <t>Poland: Gaz-System Market Information Module, 'Actual quantity of gas transmitted' per zone (https://swi.gaz-system.pl/mir/#/public/bil/ksp-realization; billing data, operative values for the latest days). Romania: Transgaz 'Physical flows' table, exit points to consumers (https://www.transgaz.ro/en/clients/operational-data/physical-flows). Finland: Gasgrid Finland 'Gas consumption in Finland' workbook (https://gasgrid.fi/en/gas-business/transparency-and-market-information/). Spain 2021-22: Enagas monthly statistical bulletin PDFs (https://www.enagas.es/en/technical-management-system/energy-data/publications/gas-statistical-bulletin/); the Enagas daily demand-history JSON used in europe_tso_gas_demand_daily.xlsx starts only in 2023. Free, no key.</t>
         </is>
       </c>
     </row>
@@ -717,29 +754,36 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GWh per gas day. DE_distribution = THE SLP (standard-profile consumers on distribution networks); DE_industry_power = THE RLM (metered large consumers: industry and gas-fired power, not split further); DE_total = both. FR_industrial = direct industrial connections, FR_distribution = public distribution (GRD/ELD), FR_power = gas-fired power plants (CCCG), FR_total = the three. ES_total = Enagás national demand. DK_total = gas delivered to Denmark from the transmission system plus biogas injected (Energinet's definition). PT_total = REN total consumption (whole GWh), split into conventional market, electricity market (gas-fired power), distribution (GRMS) and high-pressure clients. Recent days are preliminary and restated.</t>
+          <t>Sheet Daily: GWh per gas day. PL_distribution = exit to DSO networks (H and L gas); PL_final_customers = aggregated final-customer exit points; PL_other = TSO own needs, nitrogen-removal / mixing plants and aggregated PPG points; PL_total = the three; PL_dso_return = gas entering the grid back from DSO networks (information only, not netted). Exchange/OTC points, storage, interconnectors and compulsory stocks are left out. RO_final_customers = final clients connected directly to the transmission system (SM-CF001), RO_distribution = distribution systems (SM-SD001), RO_total = both (MWh at 15C/15C converted to GWh). FI_total = Gasgrid's gas consumption in Finland (GCV). These are what the transmission operators deliver to consumers: gas produced and consumed without entering the transmission grid is not included, so the totals sit about 8-10% (PL, RO) below Eurostat's gross inland consumption; Finland is 20-30% below Eurostat in 2023-25 (biomethane and distribution-connected gas).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Re-fetches the last 45 days each run plus gaps; history from 2021-01-01.</t>
+          <t>Sheet Monthly: Spain, GWh per month, from the Enagas bulletin table 'Evolution of gas demand' (month column). ES_national = national market demand = ES_conventional (conventional market, incl. industry) + ES_power (power generation); LNG vessel loading and international exports are excluded. source_file = the bulletin PDF the month was read from.</t>
         </is>
       </c>
     </row>
-    <row r="10"/>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Daily series re-fetch the last 45 days each run plus gaps; history from 2021-01-01. Bulletins already read are not downloaded again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>Last pull</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-04 01:52 UTC; 2101 days, 2021-01-01 to 2026-10-02</t>
+          <t>2026-10-04 02:05 UTC; daily 2101 days 2021-01-01 to 2026-10-02; Spain monthly 41 months 2021-02 to 2026-08</t>
         </is>
       </c>
     </row>
@@ -754,7 +798,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D70"/>
+  <dimension ref="A1:E70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -781,6 +825,11 @@
           <t>Finland</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Spain (Enagas bulletin)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="n">
@@ -809,6 +858,9 @@
       <c r="D3" t="n">
         <v>3.7038</v>
       </c>
+      <c r="E3" t="n">
+        <v>28.337</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
@@ -851,6 +903,9 @@
       <c r="D6" t="n">
         <v>1.057</v>
       </c>
+      <c r="E6" t="n">
+        <v>26.953</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="n">
@@ -865,6 +920,9 @@
       <c r="D7" t="n">
         <v>1.3103</v>
       </c>
+      <c r="E7" t="n">
+        <v>27.358</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
@@ -935,6 +993,9 @@
       <c r="D12" t="n">
         <v>1.5769</v>
       </c>
+      <c r="E12" t="n">
+        <v>40.009</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="n">
@@ -977,6 +1038,9 @@
       <c r="D15" t="n">
         <v>1.5021</v>
       </c>
+      <c r="E15" t="n">
+        <v>34.727</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="n">
@@ -991,6 +1055,9 @@
       <c r="D16" t="n">
         <v>1.5502</v>
       </c>
+      <c r="E16" t="n">
+        <v>34.131</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="n">
@@ -1061,6 +1128,9 @@
       <c r="D21" t="n">
         <v>0.7168</v>
       </c>
+      <c r="E21" t="n">
+        <v>28.372</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
@@ -1075,6 +1145,9 @@
       <c r="D22" t="n">
         <v>0.6507000000000001</v>
       </c>
+      <c r="E22" t="n">
+        <v>28.144</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
@@ -1117,6 +1190,9 @@
       <c r="D25" t="n">
         <v>1.0773</v>
       </c>
+      <c r="E25" t="n">
+        <v>28</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
@@ -1131,6 +1207,9 @@
       <c r="D26" t="n">
         <v>1.0562</v>
       </c>
+      <c r="E26" t="n">
+        <v>29.678</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
@@ -1159,6 +1238,9 @@
       <c r="D28" t="n">
         <v>1.2175</v>
       </c>
+      <c r="E28" t="n">
+        <v>28.685</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
@@ -1201,6 +1283,9 @@
       <c r="D31" t="n">
         <v>0.8813</v>
       </c>
+      <c r="E31" t="n">
+        <v>26.174</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
@@ -1243,6 +1328,9 @@
       <c r="D34" t="n">
         <v>0.972</v>
       </c>
+      <c r="E34" t="n">
+        <v>26.39</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
@@ -1257,6 +1345,9 @@
       <c r="D35" t="n">
         <v>1.2468</v>
       </c>
+      <c r="E35" t="n">
+        <v>25.068</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
@@ -1271,6 +1362,9 @@
       <c r="D36" t="n">
         <v>1.38694</v>
       </c>
+      <c r="E36" t="n">
+        <v>26.105</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
@@ -1285,6 +1379,9 @@
       <c r="D37" t="n">
         <v>1.4909</v>
       </c>
+      <c r="E37" t="n">
+        <v>30.441</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
@@ -1327,6 +1424,9 @@
       <c r="D40" t="n">
         <v>1.5599</v>
       </c>
+      <c r="E40" t="n">
+        <v>26.804</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
@@ -1383,6 +1483,9 @@
       <c r="D44" t="n">
         <v>0.8687</v>
       </c>
+      <c r="E44" t="n">
+        <v>23.647</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
@@ -1397,6 +1500,9 @@
       <c r="D45" t="n">
         <v>0.919</v>
       </c>
+      <c r="E45" t="n">
+        <v>22.67</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
@@ -1425,6 +1531,9 @@
       <c r="D47" t="n">
         <v>1.0386</v>
       </c>
+      <c r="E47" t="n">
+        <v>23.956</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
@@ -1439,6 +1548,9 @@
       <c r="D48" t="n">
         <v>1.0884</v>
       </c>
+      <c r="E48" t="n">
+        <v>29.433</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
@@ -1453,6 +1565,9 @@
       <c r="D49" t="n">
         <v>1.3121</v>
       </c>
+      <c r="E49" t="n">
+        <v>35.163</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
@@ -1467,6 +1582,9 @@
       <c r="D50" t="n">
         <v>1.5111</v>
       </c>
+      <c r="E50" t="n">
+        <v>32.802</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="n">
@@ -1481,6 +1599,9 @@
       <c r="D51" t="n">
         <v>1.416</v>
       </c>
+      <c r="E51" t="n">
+        <v>28.632</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="n">
@@ -1495,6 +1616,9 @@
       <c r="D52" t="n">
         <v>1.3686</v>
       </c>
+      <c r="E52" t="n">
+        <v>28.402</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
@@ -1509,6 +1633,9 @@
       <c r="D53" t="n">
         <v>1.1282</v>
       </c>
+      <c r="E53" t="n">
+        <v>23.09</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
@@ -1523,6 +1650,9 @@
       <c r="D54" t="n">
         <v>0.9394</v>
       </c>
+      <c r="E54" t="n">
+        <v>24.446</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
@@ -1537,6 +1667,9 @@
       <c r="D55" t="n">
         <v>0.8764</v>
       </c>
+      <c r="E55" t="n">
+        <v>25.548</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
@@ -1551,6 +1684,9 @@
       <c r="D56" t="n">
         <v>0.7024</v>
       </c>
+      <c r="E56" t="n">
+        <v>25.378</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
@@ -1565,6 +1701,9 @@
       <c r="D57" t="n">
         <v>0.7992</v>
       </c>
+      <c r="E57" t="n">
+        <v>22.982</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
@@ -1579,6 +1718,9 @@
       <c r="D58" t="n">
         <v>0.5979</v>
       </c>
+      <c r="E58" t="n">
+        <v>24.598</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
@@ -1593,6 +1735,9 @@
       <c r="D59" t="n">
         <v>0.8095</v>
       </c>
+      <c r="E59" t="n">
+        <v>29.201</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
@@ -1621,6 +1766,9 @@
       <c r="D61" t="n">
         <v>1.0487</v>
       </c>
+      <c r="E61" t="n">
+        <v>35.236</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="n">
@@ -1635,6 +1783,9 @@
       <c r="D62" t="n">
         <v>2.5011</v>
       </c>
+      <c r="E62" t="n">
+        <v>36.172</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
@@ -1649,6 +1800,9 @@
       <c r="D63" t="n">
         <v>2.402</v>
       </c>
+      <c r="E63" t="n">
+        <v>27.582</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
@@ -1663,6 +1817,9 @@
       <c r="D64" t="n">
         <v>0.7038</v>
       </c>
+      <c r="E64" t="n">
+        <v>28.765</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
@@ -1677,6 +1834,9 @@
       <c r="D65" t="n">
         <v>0.7197</v>
       </c>
+      <c r="E65" t="n">
+        <v>23.065</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
@@ -1691,6 +1851,9 @@
       <c r="D66" t="n">
         <v>0.8864</v>
       </c>
+      <c r="E66" t="n">
+        <v>24.196</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
@@ -1705,6 +1868,9 @@
       <c r="D67" t="n">
         <v>0.727</v>
       </c>
+      <c r="E67" t="n">
+        <v>23.84</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
@@ -1719,6 +1885,9 @@
       <c r="D68" t="n">
         <v>0.5988</v>
       </c>
+      <c r="E68" t="n">
+        <v>27.507</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
@@ -1732,6 +1901,9 @@
       </c>
       <c r="D69" t="n">
         <v>0.7095</v>
+      </c>
+      <c r="E69" t="n">
+        <v>25.086</v>
       </c>
     </row>
     <row r="70">
@@ -68951,4 +69123,824 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E42"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>month</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ES_national</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ES_conventional</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>ES_power</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>source_file</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n">
+        <v>44228</v>
+      </c>
+      <c r="B2" t="n">
+        <v>28337</v>
+      </c>
+      <c r="C2" t="n">
+        <v>25210</v>
+      </c>
+      <c r="D2" t="n">
+        <v>3126</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_febrero21_INGLES.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
+        <v>44317</v>
+      </c>
+      <c r="B3" t="n">
+        <v>26953</v>
+      </c>
+      <c r="C3" t="n">
+        <v>21984</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4970</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_mayo_INGLES_1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>44348</v>
+      </c>
+      <c r="B4" t="n">
+        <v>27358</v>
+      </c>
+      <c r="C4" t="n">
+        <v>20065</v>
+      </c>
+      <c r="D4" t="n">
+        <v>7293</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_junio21_INGLES.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>44501</v>
+      </c>
+      <c r="B5" t="n">
+        <v>40009</v>
+      </c>
+      <c r="C5" t="n">
+        <v>27229</v>
+      </c>
+      <c r="D5" t="n">
+        <v>12780</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Monthly-Bulletin-Gas-november-2022.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
+        <v>44593</v>
+      </c>
+      <c r="B6" t="n">
+        <v>34727</v>
+      </c>
+      <c r="C6" t="n">
+        <v>25380</v>
+      </c>
+      <c r="D6" t="n">
+        <v>9346</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Monthly-Bulletin-Gas-february-2022.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="n">
+        <v>44621</v>
+      </c>
+      <c r="B7" t="n">
+        <v>34131</v>
+      </c>
+      <c r="C7" t="n">
+        <v>26437</v>
+      </c>
+      <c r="D7" t="n">
+        <v>7695</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Monthly-Bulletin-Gas-march-2022.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>44774</v>
+      </c>
+      <c r="B8" t="n">
+        <v>28372</v>
+      </c>
+      <c r="C8" t="n">
+        <v>11731</v>
+      </c>
+      <c r="D8" t="n">
+        <v>16641</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Monthly-Bulletin-Gas-August-2022.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>44805</v>
+      </c>
+      <c r="B9" t="n">
+        <v>28144</v>
+      </c>
+      <c r="C9" t="n">
+        <v>12409</v>
+      </c>
+      <c r="D9" t="n">
+        <v>15735</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Monthly-Bulletin-Gas-September-2022.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>44896</v>
+      </c>
+      <c r="B10" t="n">
+        <v>28000</v>
+      </c>
+      <c r="C10" t="n">
+        <v>19250</v>
+      </c>
+      <c r="D10" t="n">
+        <v>8750</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Monthly-Bulletin-Gas-December-2022.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>44927</v>
+      </c>
+      <c r="B11" t="n">
+        <v>29678</v>
+      </c>
+      <c r="C11" t="n">
+        <v>23887</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5791</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Monthly-Bulletin-Gas-January-2023.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>44986</v>
+      </c>
+      <c r="B12" t="n">
+        <v>28685</v>
+      </c>
+      <c r="C12" t="n">
+        <v>22293</v>
+      </c>
+      <c r="D12" t="n">
+        <v>6393</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Monthly-Bulletin-Gas-March-2023.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>45078</v>
+      </c>
+      <c r="B13" t="n">
+        <v>26174</v>
+      </c>
+      <c r="C13" t="n">
+        <v>16673</v>
+      </c>
+      <c r="D13" t="n">
+        <v>9500</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Monthly_Bulletin_June23.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>45170</v>
+      </c>
+      <c r="B14" t="n">
+        <v>26390</v>
+      </c>
+      <c r="C14" t="n">
+        <v>16321</v>
+      </c>
+      <c r="D14" t="n">
+        <v>10068</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Monthly_bulletin_Sep23.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>45200</v>
+      </c>
+      <c r="B15" t="n">
+        <v>25068</v>
+      </c>
+      <c r="C15" t="n">
+        <v>16747</v>
+      </c>
+      <c r="D15" t="n">
+        <v>8320</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Monthly_bulletin_Oct23.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>45231</v>
+      </c>
+      <c r="B16" t="n">
+        <v>26105</v>
+      </c>
+      <c r="C16" t="n">
+        <v>19965</v>
+      </c>
+      <c r="D16" t="n">
+        <v>6140</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Monthly%20Bulletin%20Nov23.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>45261</v>
+      </c>
+      <c r="B17" t="n">
+        <v>30441</v>
+      </c>
+      <c r="C17" t="n">
+        <v>23753</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6688</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_dic23_ingles1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>45352</v>
+      </c>
+      <c r="B18" t="n">
+        <v>26804</v>
+      </c>
+      <c r="C18" t="n">
+        <v>22040</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4765</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_marzo24_ingles_1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>45474</v>
+      </c>
+      <c r="B19" t="n">
+        <v>23647</v>
+      </c>
+      <c r="C19" t="n">
+        <v>16579</v>
+      </c>
+      <c r="D19" t="n">
+        <v>7068</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_jul24_ingles.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>45505</v>
+      </c>
+      <c r="B20" t="n">
+        <v>22670</v>
+      </c>
+      <c r="C20" t="n">
+        <v>15171</v>
+      </c>
+      <c r="D20" t="n">
+        <v>7499</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_agosto24_ingles.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>45566</v>
+      </c>
+      <c r="B21" t="n">
+        <v>23956</v>
+      </c>
+      <c r="C21" t="n">
+        <v>17954</v>
+      </c>
+      <c r="D21" t="n">
+        <v>6002</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_oct24_ingles.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>45597</v>
+      </c>
+      <c r="B22" t="n">
+        <v>29433</v>
+      </c>
+      <c r="C22" t="n">
+        <v>21109</v>
+      </c>
+      <c r="D22" t="n">
+        <v>8324</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_nov24_ingles.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>45627</v>
+      </c>
+      <c r="B23" t="n">
+        <v>35163</v>
+      </c>
+      <c r="C23" t="n">
+        <v>24684</v>
+      </c>
+      <c r="D23" t="n">
+        <v>10479</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_dic24_ingles.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>45658</v>
+      </c>
+      <c r="B24" t="n">
+        <v>32802</v>
+      </c>
+      <c r="C24" t="n">
+        <v>25846</v>
+      </c>
+      <c r="D24" t="n">
+        <v>6956</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_ene25_ingles2.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>45689</v>
+      </c>
+      <c r="B25" t="n">
+        <v>28632</v>
+      </c>
+      <c r="C25" t="n">
+        <v>22088</v>
+      </c>
+      <c r="D25" t="n">
+        <v>6544</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_feb25_ingles2.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>45717</v>
+      </c>
+      <c r="B26" t="n">
+        <v>28402</v>
+      </c>
+      <c r="C26" t="n">
+        <v>23054</v>
+      </c>
+      <c r="D26" t="n">
+        <v>5348</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_mar25_ingles.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>45748</v>
+      </c>
+      <c r="B27" t="n">
+        <v>23090</v>
+      </c>
+      <c r="C27" t="n">
+        <v>17558</v>
+      </c>
+      <c r="D27" t="n">
+        <v>5532</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_abr25_ingles.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>45778</v>
+      </c>
+      <c r="B28" t="n">
+        <v>24446</v>
+      </c>
+      <c r="C28" t="n">
+        <v>17262</v>
+      </c>
+      <c r="D28" t="n">
+        <v>7185</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_may25_ingles_rev.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>45809</v>
+      </c>
+      <c r="B29" t="n">
+        <v>25548</v>
+      </c>
+      <c r="C29" t="n">
+        <v>15709</v>
+      </c>
+      <c r="D29" t="n">
+        <v>9839</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_jun25_ingles_rev.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>45839</v>
+      </c>
+      <c r="B30" t="n">
+        <v>25378</v>
+      </c>
+      <c r="C30" t="n">
+        <v>16070</v>
+      </c>
+      <c r="D30" t="n">
+        <v>9308</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_jul25_ingles_rev.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>45870</v>
+      </c>
+      <c r="B31" t="n">
+        <v>22982</v>
+      </c>
+      <c r="C31" t="n">
+        <v>13857</v>
+      </c>
+      <c r="D31" t="n">
+        <v>9125</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_ago25_ingles_rev.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>45901</v>
+      </c>
+      <c r="B32" t="n">
+        <v>24598</v>
+      </c>
+      <c r="C32" t="n">
+        <v>16139</v>
+      </c>
+      <c r="D32" t="n">
+        <v>8459</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_sep25_ingles.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>45931</v>
+      </c>
+      <c r="B33" t="n">
+        <v>29201</v>
+      </c>
+      <c r="C33" t="n">
+        <v>17887</v>
+      </c>
+      <c r="D33" t="n">
+        <v>11315</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_oct25_ingles.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B34" t="n">
+        <v>35236</v>
+      </c>
+      <c r="C34" t="n">
+        <v>24431</v>
+      </c>
+      <c r="D34" t="n">
+        <v>10805</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_dic25_ingles.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>46023</v>
+      </c>
+      <c r="B35" t="n">
+        <v>36172</v>
+      </c>
+      <c r="C35" t="n">
+        <v>27138</v>
+      </c>
+      <c r="D35" t="n">
+        <v>9034</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_ene26_inglesrev.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>46054</v>
+      </c>
+      <c r="B36" t="n">
+        <v>27582</v>
+      </c>
+      <c r="C36" t="n">
+        <v>21088</v>
+      </c>
+      <c r="D36" t="n">
+        <v>6493</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_feb26_ingles_rev.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>46082</v>
+      </c>
+      <c r="B37" t="n">
+        <v>28765</v>
+      </c>
+      <c r="C37" t="n">
+        <v>20913</v>
+      </c>
+      <c r="D37" t="n">
+        <v>7852</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_mar26_ingles_rev.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B38" t="n">
+        <v>23065</v>
+      </c>
+      <c r="C38" t="n">
+        <v>16448</v>
+      </c>
+      <c r="D38" t="n">
+        <v>6617</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_abr26_ingles.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B39" t="n">
+        <v>24196</v>
+      </c>
+      <c r="C39" t="n">
+        <v>16964</v>
+      </c>
+      <c r="D39" t="n">
+        <v>7232</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_may26_ingles.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B40" t="n">
+        <v>23840</v>
+      </c>
+      <c r="C40" t="n">
+        <v>15267</v>
+      </c>
+      <c r="D40" t="n">
+        <v>8573</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_jun26_ingles.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B41" t="n">
+        <v>27507</v>
+      </c>
+      <c r="C41" t="n">
+        <v>15263</v>
+      </c>
+      <c r="D41" t="n">
+        <v>12244</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_jul26_ingles_rev1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>46235</v>
+      </c>
+      <c r="B42" t="n">
+        <v>25086</v>
+      </c>
+      <c r="C42" t="n">
+        <v>13134</v>
+      </c>
+      <c r="D42" t="n">
+        <v>11952</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_ago26_ingles.pdf</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/output/Data and Chart Outputs/europe_tso_gas_demand_extra_daily.xlsx
+++ b/output/Data and Chart Outputs/europe_tso_gas_demand_extra_daily.xlsx
@@ -819,7 +819,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-04 02:17 UTC; daily 2102 days 2021-01-01 to 2026-10-03; Spain monthly 41 months 2021-02 to 2026-08</t>
+          <t>2026-10-04 02:29 UTC; daily 2102 days 2021-01-01 to 2026-10-03; Spain monthly 66 months 2021-01 to 2026-08</t>
         </is>
       </c>
     </row>
@@ -885,6 +885,9 @@
       <c r="D2" t="n">
         <v>3.8196</v>
       </c>
+      <c r="F2" t="n">
+        <v>38.819</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="n">
@@ -916,6 +919,9 @@
       <c r="D4" t="n">
         <v>2.9954</v>
       </c>
+      <c r="F4" t="n">
+        <v>32.173</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="n">
@@ -930,6 +936,9 @@
       <c r="D5" t="n">
         <v>1.9155</v>
       </c>
+      <c r="F5" t="n">
+        <v>30.955</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="n">
@@ -978,6 +987,9 @@
       <c r="D8" t="n">
         <v>1.4287</v>
       </c>
+      <c r="F8" t="n">
+        <v>27.839</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
@@ -995,6 +1007,9 @@
       <c r="E9" t="n">
         <v>1.8132</v>
       </c>
+      <c r="F9" t="n">
+        <v>27.209</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="n">
@@ -1012,6 +1027,9 @@
       <c r="E10" t="n">
         <v>1.74771</v>
       </c>
+      <c r="F10" t="n">
+        <v>30.263</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="n">
@@ -1029,6 +1047,9 @@
       <c r="E11" t="n">
         <v>2.487</v>
       </c>
+      <c r="F11" t="n">
+        <v>29.683</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="n">
@@ -1066,6 +1087,9 @@
       <c r="E13" t="n">
         <v>2.97209</v>
       </c>
+      <c r="F13" t="n">
+        <v>38.698</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="n">
@@ -1083,6 +1107,9 @@
       <c r="E14" t="n">
         <v>3.42487</v>
       </c>
+      <c r="F14" t="n">
+        <v>41.926</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="n">
@@ -1140,6 +1167,9 @@
       <c r="E17" t="n">
         <v>1.93069</v>
       </c>
+      <c r="F17" t="n">
+        <v>26.895</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
@@ -1157,6 +1187,9 @@
       <c r="E18" t="n">
         <v>1.2703</v>
       </c>
+      <c r="F18" t="n">
+        <v>25.714</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
@@ -1174,6 +1207,9 @@
       <c r="E19" t="n">
         <v>1.23353</v>
       </c>
+      <c r="F19" t="n">
+        <v>29.15</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
@@ -1191,6 +1227,9 @@
       <c r="E20" t="n">
         <v>1.50214</v>
       </c>
+      <c r="F20" t="n">
+        <v>31.174</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
@@ -1248,6 +1287,9 @@
       <c r="E23" t="n">
         <v>1.77219</v>
       </c>
+      <c r="F23" t="n">
+        <v>28.038</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
@@ -1265,6 +1307,9 @@
       <c r="E24" t="n">
         <v>2.25606</v>
       </c>
+      <c r="F24" t="n">
+        <v>28.013</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
@@ -1322,6 +1367,9 @@
       <c r="E27" t="n">
         <v>2.74328</v>
       </c>
+      <c r="F27" t="n">
+        <v>33.528</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
@@ -1359,6 +1407,9 @@
       <c r="E29" t="n">
         <v>2.14647</v>
       </c>
+      <c r="F29" t="n">
+        <v>23.728</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
@@ -1376,6 +1427,9 @@
       <c r="E30" t="n">
         <v>1.5429</v>
       </c>
+      <c r="F30" t="n">
+        <v>24.536</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
@@ -1413,6 +1467,9 @@
       <c r="E32" t="n">
         <v>1.72327</v>
       </c>
+      <c r="F32" t="n">
+        <v>26.199</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
@@ -1430,6 +1487,9 @@
       <c r="E33" t="n">
         <v>1.70887</v>
       </c>
+      <c r="F33" t="n">
+        <v>25.073</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
@@ -1527,6 +1587,9 @@
       <c r="E38" t="n">
         <v>3.24127</v>
       </c>
+      <c r="F38" t="n">
+        <v>33.606</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
@@ -1544,6 +1607,9 @@
       <c r="E39" t="n">
         <v>2.30447</v>
       </c>
+      <c r="F39" t="n">
+        <v>27.83</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
@@ -1581,6 +1647,9 @@
       <c r="E41" t="n">
         <v>1.60349</v>
       </c>
+      <c r="F41" t="n">
+        <v>22.557</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
@@ -1598,6 +1667,9 @@
       <c r="E42" t="n">
         <v>1.32939</v>
       </c>
+      <c r="F42" t="n">
+        <v>22.455</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
@@ -1614,6 +1686,9 @@
       </c>
       <c r="E43" t="n">
         <v>1.02916</v>
+      </c>
+      <c r="F43" t="n">
+        <v>20.98</v>
       </c>
     </row>
     <row r="44">
@@ -86388,7 +86463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86420,778 +86495,1253 @@
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
+        <v>44197</v>
+      </c>
+      <c r="B2" t="n">
+        <v>38819</v>
+      </c>
+      <c r="C2" t="n">
+        <v>33161</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5657</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_enero21_INGLES_rev2.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="n">
         <v>44228</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B3" t="n">
         <v>28337</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C3" t="n">
         <v>25210</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D3" t="n">
         <v>3126</v>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_febrero21_INGLES.pdf</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="n">
+    <row r="4">
+      <c r="A4" s="4" t="n">
+        <v>44256</v>
+      </c>
+      <c r="B4" t="n">
+        <v>32173</v>
+      </c>
+      <c r="C4" t="n">
+        <v>27792</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4381</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_marzo21_INGLES_rev3.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n">
+        <v>44287</v>
+      </c>
+      <c r="B5" t="n">
+        <v>30955</v>
+      </c>
+      <c r="C5" t="n">
+        <v>24222</v>
+      </c>
+      <c r="D5" t="n">
+        <v>6733</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_abril21_INGLES_1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n">
         <v>44317</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B6" t="n">
         <v>26953</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C6" t="n">
         <v>21984</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D6" t="n">
         <v>4970</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_mayo_INGLES_1.pdf</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="4" t="n">
+    <row r="7">
+      <c r="A7" s="4" t="n">
         <v>44348</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B7" t="n">
         <v>27358</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C7" t="n">
         <v>20065</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D7" t="n">
         <v>7293</v>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_junio21_INGLES.pdf</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="n">
+    <row r="8">
+      <c r="A8" s="4" t="n">
+        <v>44378</v>
+      </c>
+      <c r="B8" t="n">
+        <v>27839</v>
+      </c>
+      <c r="C8" t="n">
+        <v>20232</v>
+      </c>
+      <c r="D8" t="n">
+        <v>7607</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_julio21_INGLES_REV.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="n">
+        <v>44409</v>
+      </c>
+      <c r="B9" t="n">
+        <v>27209</v>
+      </c>
+      <c r="C9" t="n">
+        <v>18801</v>
+      </c>
+      <c r="D9" t="n">
+        <v>8408</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_agosto21_INGLES_rev.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>44440</v>
+      </c>
+      <c r="B10" t="n">
+        <v>30263</v>
+      </c>
+      <c r="C10" t="n">
+        <v>20069</v>
+      </c>
+      <c r="D10" t="n">
+        <v>10194</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Monthly-Bulletin-Gas-september-2021..pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>44470</v>
+      </c>
+      <c r="B11" t="n">
+        <v>29683</v>
+      </c>
+      <c r="C11" t="n">
+        <v>20829</v>
+      </c>
+      <c r="D11" t="n">
+        <v>8853</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Monthly-Bulletin-Gas-october-2021.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
         <v>44501</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B12" t="n">
         <v>40009</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C12" t="n">
         <v>27229</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D12" t="n">
         <v>12780</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>Monthly-Bulletin-Gas-november-2022.pdf</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="4" t="n">
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>44531</v>
+      </c>
+      <c r="B13" t="n">
+        <v>38698</v>
+      </c>
+      <c r="C13" t="n">
+        <v>28447</v>
+      </c>
+      <c r="D13" t="n">
+        <v>10251</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Monthly-Bulletin-Gas-december-2022.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>44562</v>
+      </c>
+      <c r="B14" t="n">
+        <v>41926</v>
+      </c>
+      <c r="C14" t="n">
+        <v>30236</v>
+      </c>
+      <c r="D14" t="n">
+        <v>11689</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Monthly-Bulletin-Gas-january-2022.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
         <v>44593</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B15" t="n">
         <v>34727</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C15" t="n">
         <v>25380</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D15" t="n">
         <v>9346</v>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>Monthly-Bulletin-Gas-february-2022.pdf</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="n">
+    <row r="16">
+      <c r="A16" s="4" t="n">
         <v>44621</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B16" t="n">
         <v>34131</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C16" t="n">
         <v>26437</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D16" t="n">
         <v>7695</v>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>Monthly-Bulletin-Gas-march-2022.pdf</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="4" t="n">
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>44652</v>
+      </c>
+      <c r="B17" t="n">
+        <v>26895</v>
+      </c>
+      <c r="C17" t="n">
+        <v>20491</v>
+      </c>
+      <c r="D17" t="n">
+        <v>6404</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Monthly-Bulletin-Gas-april-2022.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>44682</v>
+      </c>
+      <c r="B18" t="n">
+        <v>25714</v>
+      </c>
+      <c r="C18" t="n">
+        <v>18214</v>
+      </c>
+      <c r="D18" t="n">
+        <v>7500</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Monthly-Bulletin-Gas-may-2022.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>44713</v>
+      </c>
+      <c r="B19" t="n">
+        <v>29150</v>
+      </c>
+      <c r="C19" t="n">
+        <v>16025</v>
+      </c>
+      <c r="D19" t="n">
+        <v>13126</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Monthly-Bulletin-Gas-June-2022.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>44743</v>
+      </c>
+      <c r="B20" t="n">
+        <v>31174</v>
+      </c>
+      <c r="C20" t="n">
+        <v>13979</v>
+      </c>
+      <c r="D20" t="n">
+        <v>17195</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Monthly-Bulletin-Gas-July-2022.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
         <v>44774</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B21" t="n">
         <v>28372</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C21" t="n">
         <v>11731</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D21" t="n">
         <v>16641</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>Monthly-Bulletin-Gas-August-2022.pdf</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="4" t="n">
+    <row r="22">
+      <c r="A22" s="4" t="n">
         <v>44805</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B22" t="n">
         <v>28144</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C22" t="n">
         <v>12409</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D22" t="n">
         <v>15735</v>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Monthly-Bulletin-Gas-September-2022.pdf</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="4" t="n">
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>44835</v>
+      </c>
+      <c r="B23" t="n">
+        <v>28038</v>
+      </c>
+      <c r="C23" t="n">
+        <v>13711</v>
+      </c>
+      <c r="D23" t="n">
+        <v>14327</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Monthly-Bulletin-Gas-October-2022.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>44866</v>
+      </c>
+      <c r="B24" t="n">
+        <v>28013</v>
+      </c>
+      <c r="C24" t="n">
+        <v>18491</v>
+      </c>
+      <c r="D24" t="n">
+        <v>9522</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Monthly-Bulletin-Gas-November-2022.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
         <v>44896</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B25" t="n">
         <v>28000</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C25" t="n">
         <v>19250</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D25" t="n">
         <v>8750</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>Monthly-Bulletin-Gas-December-2022.pdf</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
+    <row r="26">
+      <c r="A26" s="4" t="n">
         <v>44927</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B26" t="n">
         <v>29678</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C26" t="n">
         <v>23887</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D26" t="n">
         <v>5791</v>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>Monthly-Bulletin-Gas-January-2023.pdf</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="4" t="n">
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>44958</v>
+      </c>
+      <c r="B27" t="n">
+        <v>33528</v>
+      </c>
+      <c r="C27" t="n">
+        <v>24516</v>
+      </c>
+      <c r="D27" t="n">
+        <v>9012</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Monthly-Bulletin-Gas-February-2023.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
         <v>44986</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B28" t="n">
         <v>28685</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C28" t="n">
         <v>22293</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D28" t="n">
         <v>6393</v>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>Monthly-Bulletin-Gas-March-2023.pdf</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="n">
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>45017</v>
+      </c>
+      <c r="B29" t="n">
+        <v>23728</v>
+      </c>
+      <c r="C29" t="n">
+        <v>17747</v>
+      </c>
+      <c r="D29" t="n">
+        <v>5982</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Monthly-Bulletin-Gas-April-2023.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>45047</v>
+      </c>
+      <c r="B30" t="n">
+        <v>24536</v>
+      </c>
+      <c r="C30" t="n">
+        <v>17606</v>
+      </c>
+      <c r="D30" t="n">
+        <v>6929</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Monthly%20Bulletin%20Gas%20May%202023.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
         <v>45078</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B31" t="n">
         <v>26174</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C31" t="n">
         <v>16673</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D31" t="n">
         <v>9500</v>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>Monthly_Bulletin_June23.pdf</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="n">
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>45108</v>
+      </c>
+      <c r="B32" t="n">
+        <v>26199</v>
+      </c>
+      <c r="C32" t="n">
+        <v>15763</v>
+      </c>
+      <c r="D32" t="n">
+        <v>10436</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Monthly%20Bulletin%20July23.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>45139</v>
+      </c>
+      <c r="B33" t="n">
+        <v>25073</v>
+      </c>
+      <c r="C33" t="n">
+        <v>14609</v>
+      </c>
+      <c r="D33" t="n">
+        <v>10464</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Monthly_bulletin_Aug23.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
         <v>45170</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B34" t="n">
         <v>26390</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C34" t="n">
         <v>16321</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D34" t="n">
         <v>10068</v>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>Monthly_bulletin_Sep23.pdf</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="n">
+    <row r="35">
+      <c r="A35" s="4" t="n">
         <v>45200</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B35" t="n">
         <v>25068</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C35" t="n">
         <v>16747</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D35" t="n">
         <v>8320</v>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>Monthly_bulletin_Oct23.pdf</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="4" t="n">
+    <row r="36">
+      <c r="A36" s="4" t="n">
         <v>45231</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B36" t="n">
         <v>26105</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C36" t="n">
         <v>19965</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D36" t="n">
         <v>6140</v>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>Monthly%20Bulletin%20Nov23.pdf</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="n">
+    <row r="37">
+      <c r="A37" s="4" t="n">
         <v>45261</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B37" t="n">
         <v>30441</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C37" t="n">
         <v>23753</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D37" t="n">
         <v>6688</v>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_dic23_ingles1.pdf</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="4" t="n">
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>45292</v>
+      </c>
+      <c r="B38" t="n">
+        <v>33606</v>
+      </c>
+      <c r="C38" t="n">
+        <v>26726</v>
+      </c>
+      <c r="D38" t="n">
+        <v>6880</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_ene24_ingles.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>45323</v>
+      </c>
+      <c r="B39" t="n">
+        <v>27830</v>
+      </c>
+      <c r="C39" t="n">
+        <v>23374</v>
+      </c>
+      <c r="D39" t="n">
+        <v>4456</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_feb24_ingles.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
         <v>45352</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B40" t="n">
         <v>26804</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C40" t="n">
         <v>22040</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D40" t="n">
         <v>4765</v>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_marzo24_ingles_1.pdf</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="4" t="n">
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>45383</v>
+      </c>
+      <c r="B41" t="n">
+        <v>22557</v>
+      </c>
+      <c r="C41" t="n">
+        <v>18110</v>
+      </c>
+      <c r="D41" t="n">
+        <v>4447</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_abr24_ingles_rev.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>45413</v>
+      </c>
+      <c r="B42" t="n">
+        <v>22455</v>
+      </c>
+      <c r="C42" t="n">
+        <v>18181</v>
+      </c>
+      <c r="D42" t="n">
+        <v>4274</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_mayo22_ingles_rev1.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>45444</v>
+      </c>
+      <c r="B43" t="n">
+        <v>20980</v>
+      </c>
+      <c r="C43" t="n">
+        <v>16486</v>
+      </c>
+      <c r="D43" t="n">
+        <v>4494</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_jun24_ingles.pptx.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
         <v>45474</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B44" t="n">
         <v>23647</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C44" t="n">
         <v>16579</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D44" t="n">
         <v>7068</v>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E44" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_jul24_ingles.pdf</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="4" t="n">
+    <row r="45">
+      <c r="A45" s="4" t="n">
         <v>45505</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B45" t="n">
         <v>22670</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C45" t="n">
         <v>15171</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D45" t="n">
         <v>7499</v>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_agosto24_ingles.pdf</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="4" t="n">
+    <row r="46">
+      <c r="A46" s="4" t="n">
         <v>45566</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B46" t="n">
         <v>23956</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C46" t="n">
         <v>17954</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D46" t="n">
         <v>6002</v>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E46" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_oct24_ingles.pdf</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="4" t="n">
+    <row r="47">
+      <c r="A47" s="4" t="n">
         <v>45597</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B47" t="n">
         <v>29433</v>
       </c>
-      <c r="C22" t="n">
+      <c r="C47" t="n">
         <v>21109</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D47" t="n">
         <v>8324</v>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_nov24_ingles.pdf</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="n">
+    <row r="48">
+      <c r="A48" s="4" t="n">
         <v>45627</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B48" t="n">
         <v>35163</v>
       </c>
-      <c r="C23" t="n">
+      <c r="C48" t="n">
         <v>24684</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D48" t="n">
         <v>10479</v>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_dic24_ingles.pdf</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="4" t="n">
+    <row r="49">
+      <c r="A49" s="4" t="n">
         <v>45658</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B49" t="n">
         <v>32802</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C49" t="n">
         <v>25846</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D49" t="n">
         <v>6956</v>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_ene25_ingles2.pdf</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="n">
+    <row r="50">
+      <c r="A50" s="4" t="n">
         <v>45689</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B50" t="n">
         <v>28632</v>
       </c>
-      <c r="C25" t="n">
+      <c r="C50" t="n">
         <v>22088</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D50" t="n">
         <v>6544</v>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_feb25_ingles2.pdf</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="4" t="n">
+    <row r="51">
+      <c r="A51" s="4" t="n">
         <v>45717</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B51" t="n">
         <v>28402</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C51" t="n">
         <v>23054</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D51" t="n">
         <v>5348</v>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_mar25_ingles.pdf</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="4" t="n">
+    <row r="52">
+      <c r="A52" s="4" t="n">
         <v>45748</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B52" t="n">
         <v>23090</v>
       </c>
-      <c r="C27" t="n">
+      <c r="C52" t="n">
         <v>17558</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D52" t="n">
         <v>5532</v>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_abr25_ingles.pdf</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="4" t="n">
+    <row r="53">
+      <c r="A53" s="4" t="n">
         <v>45778</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B53" t="n">
         <v>24446</v>
       </c>
-      <c r="C28" t="n">
+      <c r="C53" t="n">
         <v>17262</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D53" t="n">
         <v>7185</v>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_may25_ingles_rev.pdf</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="4" t="n">
+    <row r="54">
+      <c r="A54" s="4" t="n">
         <v>45809</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B54" t="n">
         <v>25548</v>
       </c>
-      <c r="C29" t="n">
+      <c r="C54" t="n">
         <v>15709</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D54" t="n">
         <v>9839</v>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_jun25_ingles_rev.pdf</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="4" t="n">
+    <row r="55">
+      <c r="A55" s="4" t="n">
         <v>45839</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B55" t="n">
         <v>25378</v>
       </c>
-      <c r="C30" t="n">
+      <c r="C55" t="n">
         <v>16070</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D55" t="n">
         <v>9308</v>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_jul25_ingles_rev.pdf</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="n">
+    <row r="56">
+      <c r="A56" s="4" t="n">
         <v>45870</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B56" t="n">
         <v>22982</v>
       </c>
-      <c r="C31" t="n">
+      <c r="C56" t="n">
         <v>13857</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D56" t="n">
         <v>9125</v>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_ago25_ingles_rev.pdf</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="4" t="n">
+    <row r="57">
+      <c r="A57" s="4" t="n">
         <v>45901</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B57" t="n">
         <v>24598</v>
       </c>
-      <c r="C32" t="n">
+      <c r="C57" t="n">
         <v>16139</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D57" t="n">
         <v>8459</v>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_sep25_ingles.pdf</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="n">
+    <row r="58">
+      <c r="A58" s="4" t="n">
         <v>45931</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B58" t="n">
         <v>29201</v>
       </c>
-      <c r="C33" t="n">
+      <c r="C58" t="n">
         <v>17887</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D58" t="n">
         <v>11315</v>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_oct25_ingles.pdf</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="4" t="n">
+    <row r="59">
+      <c r="A59" s="4" t="n">
         <v>45992</v>
       </c>
-      <c r="B34" t="n">
+      <c r="B59" t="n">
         <v>35236</v>
       </c>
-      <c r="C34" t="n">
+      <c r="C59" t="n">
         <v>24431</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D59" t="n">
         <v>10805</v>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_dic25_ingles.pdf</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="n">
+    <row r="60">
+      <c r="A60" s="4" t="n">
         <v>46023</v>
       </c>
-      <c r="B35" t="n">
+      <c r="B60" t="n">
         <v>36172</v>
       </c>
-      <c r="C35" t="n">
+      <c r="C60" t="n">
         <v>27138</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D60" t="n">
         <v>9034</v>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_ene26_inglesrev.pdf</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="4" t="n">
+    <row r="61">
+      <c r="A61" s="4" t="n">
         <v>46054</v>
       </c>
-      <c r="B36" t="n">
+      <c r="B61" t="n">
         <v>27582</v>
       </c>
-      <c r="C36" t="n">
+      <c r="C61" t="n">
         <v>21088</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D61" t="n">
         <v>6493</v>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_feb26_ingles_rev.pdf</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="4" t="n">
+    <row r="62">
+      <c r="A62" s="4" t="n">
         <v>46082</v>
       </c>
-      <c r="B37" t="n">
+      <c r="B62" t="n">
         <v>28765</v>
       </c>
-      <c r="C37" t="n">
+      <c r="C62" t="n">
         <v>20913</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D62" t="n">
         <v>7852</v>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_mar26_ingles_rev.pdf</t>
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="4" t="n">
+    <row r="63">
+      <c r="A63" s="4" t="n">
         <v>46113</v>
       </c>
-      <c r="B38" t="n">
+      <c r="B63" t="n">
         <v>23065</v>
       </c>
-      <c r="C38" t="n">
+      <c r="C63" t="n">
         <v>16448</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D63" t="n">
         <v>6617</v>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_abr26_ingles.pdf</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="4" t="n">
+    <row r="64">
+      <c r="A64" s="4" t="n">
         <v>46143</v>
       </c>
-      <c r="B39" t="n">
+      <c r="B64" t="n">
         <v>24196</v>
       </c>
-      <c r="C39" t="n">
+      <c r="C64" t="n">
         <v>16964</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D64" t="n">
         <v>7232</v>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_may26_ingles.pdf</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="4" t="n">
+    <row r="65">
+      <c r="A65" s="4" t="n">
         <v>46174</v>
       </c>
-      <c r="B40" t="n">
+      <c r="B65" t="n">
         <v>23840</v>
       </c>
-      <c r="C40" t="n">
+      <c r="C65" t="n">
         <v>15267</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D65" t="n">
         <v>8573</v>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_jun26_ingles.pdf</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="4" t="n">
+    <row r="66">
+      <c r="A66" s="4" t="n">
         <v>46204</v>
       </c>
-      <c r="B41" t="n">
+      <c r="B66" t="n">
         <v>27507</v>
       </c>
-      <c r="C41" t="n">
+      <c r="C66" t="n">
         <v>15263</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D66" t="n">
         <v>12244</v>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_jul26_ingles_rev1.pdf</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="4" t="n">
+    <row r="67">
+      <c r="A67" s="4" t="n">
         <v>46235</v>
       </c>
-      <c r="B42" t="n">
+      <c r="B67" t="n">
         <v>25086</v>
       </c>
-      <c r="C42" t="n">
+      <c r="C67" t="n">
         <v>13134</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D67" t="n">
         <v>11952</v>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_ago26_ingles.pdf</t>
         </is>

--- a/output/Data and Chart Outputs/europe_tso_gas_demand_extra_daily.xlsx
+++ b/output/Data and Chart Outputs/europe_tso_gas_demand_extra_daily.xlsx
@@ -819,7 +819,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-04 02:29 UTC; daily 2102 days 2021-01-01 to 2026-10-03; Spain monthly 66 months 2021-01 to 2026-08</t>
+          <t>2026-10-05 03:16 UTC; daily 2103 days 2021-01-01 to 2026-10-04; Spain monthly 66 months 2021-01 to 2026-08</t>
         </is>
       </c>
     </row>
@@ -2231,7 +2231,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2103"/>
+  <dimension ref="A1:M2104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86442,14 +86442,52 @@
       <c r="A2103" s="4" t="n">
         <v>46298</v>
       </c>
+      <c r="B2103" t="n">
+        <v>272.74</v>
+      </c>
+      <c r="C2103" t="n">
+        <v>110.92</v>
+      </c>
+      <c r="D2103" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="E2103" t="n">
+        <v>385.19</v>
+      </c>
+      <c r="F2103" t="n">
+        <v>6.03</v>
+      </c>
+      <c r="G2103" t="n">
+        <v>57.26</v>
+      </c>
+      <c r="H2103" t="n">
+        <v>96.7</v>
+      </c>
+      <c r="I2103" t="n">
+        <v>153.96</v>
+      </c>
       <c r="J2103" t="n">
-        <v>9.470000000000001</v>
+        <v>17.28</v>
       </c>
       <c r="K2103" t="n">
-        <v>11.87</v>
+        <v>24.32</v>
       </c>
       <c r="L2103" t="n">
-        <v>21.34</v>
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="J2104" t="n">
+        <v>8.779999999999999</v>
+      </c>
+      <c r="K2104" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="L2104" t="n">
+        <v>20.51</v>
       </c>
     </row>
   </sheetData>
@@ -86463,7 +86501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E67"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86492,6 +86530,11 @@
           <t>source_file</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ES_lng_trucks</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n">
@@ -86568,6 +86611,9 @@
           <t>Boletín%20Estadístico_abril21_INGLES_1.pdf</t>
         </is>
       </c>
+      <c r="F5" t="n">
+        <v>1162</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
@@ -86587,6 +86633,9 @@
           <t>Boletín%20Estadístico_mayo_INGLES_1.pdf</t>
         </is>
       </c>
+      <c r="F6" t="n">
+        <v>1162</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
@@ -86606,6 +86655,9 @@
           <t>Boletín%20Estadístico_junio21_INGLES.pdf</t>
         </is>
       </c>
+      <c r="F7" t="n">
+        <v>1133</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
@@ -86625,6 +86677,9 @@
           <t>Boletín%20Estadístico_julio21_INGLES_REV.pdf</t>
         </is>
       </c>
+      <c r="F8" t="n">
+        <v>1157</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
@@ -86644,6 +86699,9 @@
           <t>Boletín%20Estadístico_agosto21_INGLES_rev.pdf</t>
         </is>
       </c>
+      <c r="F9" t="n">
+        <v>1173</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
@@ -86663,6 +86721,9 @@
           <t>Monthly-Bulletin-Gas-september-2021..pdf</t>
         </is>
       </c>
+      <c r="F10" t="n">
+        <v>1169</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
@@ -86739,6 +86800,9 @@
           <t>Monthly-Bulletin-Gas-january-2022.pdf</t>
         </is>
       </c>
+      <c r="F14" t="n">
+        <v>1146</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
@@ -86796,6 +86860,9 @@
           <t>Monthly-Bulletin-Gas-april-2022.pdf</t>
         </is>
       </c>
+      <c r="F17" t="n">
+        <v>833</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -86815,6 +86882,9 @@
           <t>Monthly-Bulletin-Gas-may-2022.pdf</t>
         </is>
       </c>
+      <c r="F18" t="n">
+        <v>850</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
@@ -86834,6 +86904,9 @@
           <t>Monthly-Bulletin-Gas-June-2022.pdf</t>
         </is>
       </c>
+      <c r="F19" t="n">
+        <v>1133</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
@@ -86853,6 +86926,9 @@
           <t>Monthly-Bulletin-Gas-July-2022.pdf</t>
         </is>
       </c>
+      <c r="F20" t="n">
+        <v>1157</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
@@ -86929,6 +87005,9 @@
           <t>Monthly-Bulletin-Gas-November-2022.pdf</t>
         </is>
       </c>
+      <c r="F24" t="n">
+        <v>932</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
@@ -86967,6 +87046,9 @@
           <t>Monthly-Bulletin-Gas-January-2023.pdf</t>
         </is>
       </c>
+      <c r="F26" t="n">
+        <v>958</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
@@ -87157,6 +87239,9 @@
           <t>Monthly%20Bulletin%20Nov23.pdf</t>
         </is>
       </c>
+      <c r="F36" t="n">
+        <v>1017</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="n">
@@ -87290,6 +87375,9 @@
           <t>Boletín%20Estadístico_jun24_ingles.pptx.pdf</t>
         </is>
       </c>
+      <c r="F43" t="n">
+        <v>902</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="n">
@@ -87366,6 +87454,9 @@
           <t>Boletín%20Estadístico_nov24_ingles.pdf</t>
         </is>
       </c>
+      <c r="F47" t="n">
+        <v>1041</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="n">
@@ -87385,6 +87476,9 @@
           <t>Boletín%20Estadístico_dic24_ingles.pdf</t>
         </is>
       </c>
+      <c r="F48" t="n">
+        <v>1065</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="n">
@@ -87404,6 +87498,9 @@
           <t>Boletín%20Estadístico_ene25_ingles2.pdf</t>
         </is>
       </c>
+      <c r="F49" t="n">
+        <v>1143</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="n">
@@ -87423,6 +87520,9 @@
           <t>Boletín%20Estadístico_feb25_ingles2.pdf</t>
         </is>
       </c>
+      <c r="F50" t="n">
+        <v>1032</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="n">
@@ -87442,6 +87542,9 @@
           <t>Boletín%20Estadístico_mar25_ingles.pdf</t>
         </is>
       </c>
+      <c r="F51" t="n">
+        <v>1094</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="n">
@@ -87461,6 +87564,9 @@
           <t>Boletín%20Estadístico_abr25_ingles.pdf</t>
         </is>
       </c>
+      <c r="F52" t="n">
+        <v>928</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="n">
@@ -87480,6 +87586,9 @@
           <t>Boletín%20Estadístico_may25_ingles_rev.pdf</t>
         </is>
       </c>
+      <c r="F53" t="n">
+        <v>1005</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="4" t="n">
@@ -87499,6 +87608,9 @@
           <t>Boletín%20Estadístico_jun25_ingles_rev.pdf</t>
         </is>
       </c>
+      <c r="F54" t="n">
+        <v>935</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="4" t="n">
@@ -87518,6 +87630,9 @@
           <t>Boletín%20Estadístico_jul25_ingles_rev.pdf</t>
         </is>
       </c>
+      <c r="F55" t="n">
+        <v>988</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="4" t="n">
@@ -87537,6 +87652,9 @@
           <t>Boletín%20Estadístico_ago25_ingles_rev.pdf</t>
         </is>
       </c>
+      <c r="F56" t="n">
+        <v>954</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="n">
@@ -87556,6 +87674,9 @@
           <t>Boletín%20Estadístico_sep25_ingles.pdf</t>
         </is>
       </c>
+      <c r="F57" t="n">
+        <v>1075</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="4" t="n">
@@ -87575,6 +87696,9 @@
           <t>Boletín%20Estadístico_oct25_ingles.pdf</t>
         </is>
       </c>
+      <c r="F58" t="n">
+        <v>1107</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="4" t="n">
@@ -87594,6 +87718,9 @@
           <t>Boletín%20Estadístico_dic25_ingles.pdf</t>
         </is>
       </c>
+      <c r="F59" t="n">
+        <v>1122</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
@@ -87632,6 +87759,9 @@
           <t>Boletín%20Estadístico_feb26_ingles_rev.pdf</t>
         </is>
       </c>
+      <c r="F61" t="n">
+        <v>1059</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">
@@ -87651,6 +87781,9 @@
           <t>Boletín%20Estadístico_mar26_ingles_rev.pdf</t>
         </is>
       </c>
+      <c r="F62" t="n">
+        <v>1116</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="n">
@@ -87670,6 +87803,9 @@
           <t>Boletín%20Estadístico_abr26_ingles.pdf</t>
         </is>
       </c>
+      <c r="F63" t="n">
+        <v>952</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="4" t="n">
@@ -87689,6 +87825,9 @@
           <t>Boletín%20Estadístico_may26_ingles.pdf</t>
         </is>
       </c>
+      <c r="F64" t="n">
+        <v>957</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="n">
@@ -87708,6 +87847,9 @@
           <t>Boletín%20Estadístico_jun26_ingles.pdf</t>
         </is>
       </c>
+      <c r="F65" t="n">
+        <v>947</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="4" t="n">
@@ -87727,6 +87869,9 @@
           <t>Boletín%20Estadístico_jul26_ingles_rev1.pdf</t>
         </is>
       </c>
+      <c r="F66" t="n">
+        <v>1012</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="4" t="n">
@@ -87746,6 +87891,9 @@
           <t>Boletín%20Estadístico_ago26_ingles.pdf</t>
         </is>
       </c>
+      <c r="F67" t="n">
+        <v>948</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/Data and Chart Outputs/europe_tso_gas_demand_extra_daily.xlsx
+++ b/output/Data and Chart Outputs/europe_tso_gas_demand_extra_daily.xlsx
@@ -819,7 +819,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-05 03:16 UTC; daily 2103 days 2021-01-01 to 2026-10-04; Spain monthly 66 months 2021-01 to 2026-08</t>
+          <t>2026-10-05 03:32 UTC; daily 2103 days 2021-01-01 to 2026-10-04; Spain monthly 67 months 2021-01 to 2026-08</t>
         </is>
       </c>
     </row>
@@ -86501,7 +86501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86554,6 +86554,9 @@
           <t>Boletín%20Estadístico_enero21_INGLES_rev2.pdf</t>
         </is>
       </c>
+      <c r="F2" t="n">
+        <v>1330</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="n">
@@ -86762,6 +86765,9 @@
           <t>Monthly-Bulletin-Gas-november-2022.pdf</t>
         </is>
       </c>
+      <c r="F12" t="n">
+        <v>1286</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
@@ -87144,6 +87150,9 @@
           <t>Monthly_Bulletin_June23.pdf</t>
         </is>
       </c>
+      <c r="F31" t="n">
+        <v>937</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -87261,6 +87270,9 @@
           <t>Boletín%20Estadístico_dic23_ingles1.pdf</t>
         </is>
       </c>
+      <c r="F37" t="n">
+        <v>1010</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="n">
@@ -87280,6 +87292,9 @@
           <t>Boletín%20Estadístico_ene24_ingles.pdf</t>
         </is>
       </c>
+      <c r="F38" t="n">
+        <v>1161</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="n">
@@ -87299,6 +87314,9 @@
           <t>Boletín%20Estadístico_feb24_ingles.pdf</t>
         </is>
       </c>
+      <c r="F39" t="n">
+        <v>1078</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="n">
@@ -87318,6 +87336,9 @@
           <t>Boletín%20Estadístico_marzo24_ingles_1.pdf</t>
         </is>
       </c>
+      <c r="F40" t="n">
+        <v>1048</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="n">
@@ -87337,6 +87358,9 @@
           <t>Boletín%20Estadístico_abr24_ingles_rev.pdf</t>
         </is>
       </c>
+      <c r="F41" t="n">
+        <v>1004</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="n">
@@ -87356,6 +87380,9 @@
           <t>Boletín%20Estadístico_mayo22_ingles_rev1.pdf</t>
         </is>
       </c>
+      <c r="F42" t="n">
+        <v>1009</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -87397,6 +87424,9 @@
           <t>Boletín%20Estadístico_jul24_ingles.pdf</t>
         </is>
       </c>
+      <c r="F44" t="n">
+        <v>1053</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="n">
@@ -87416,482 +87446,496 @@
           <t>Boletín%20Estadístico_agosto24_ingles.pdf</t>
         </is>
       </c>
+      <c r="F45" t="n">
+        <v>1006</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="n">
+        <v>45536</v>
+      </c>
+      <c r="F46" t="n">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
         <v>45566</v>
       </c>
-      <c r="B46" t="n">
+      <c r="B47" t="n">
         <v>23956</v>
       </c>
-      <c r="C46" t="n">
+      <c r="C47" t="n">
         <v>17954</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D47" t="n">
         <v>6002</v>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_oct24_ingles.pdf</t>
         </is>
       </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="n">
+      <c r="F47" t="n">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
         <v>45597</v>
       </c>
-      <c r="B47" t="n">
+      <c r="B48" t="n">
         <v>29433</v>
       </c>
-      <c r="C47" t="n">
+      <c r="C48" t="n">
         <v>21109</v>
       </c>
-      <c r="D47" t="n">
+      <c r="D48" t="n">
         <v>8324</v>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="E48" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_nov24_ingles.pdf</t>
         </is>
       </c>
-      <c r="F47" t="n">
+      <c r="F48" t="n">
         <v>1041</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="4" t="n">
+    <row r="49">
+      <c r="A49" s="4" t="n">
         <v>45627</v>
       </c>
-      <c r="B48" t="n">
+      <c r="B49" t="n">
         <v>35163</v>
       </c>
-      <c r="C48" t="n">
+      <c r="C49" t="n">
         <v>24684</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D49" t="n">
         <v>10479</v>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_dic24_ingles.pdf</t>
         </is>
       </c>
-      <c r="F48" t="n">
+      <c r="F49" t="n">
         <v>1065</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="4" t="n">
+    <row r="50">
+      <c r="A50" s="4" t="n">
         <v>45658</v>
       </c>
-      <c r="B49" t="n">
+      <c r="B50" t="n">
         <v>32802</v>
       </c>
-      <c r="C49" t="n">
+      <c r="C50" t="n">
         <v>25846</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D50" t="n">
         <v>6956</v>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_ene25_ingles2.pdf</t>
         </is>
       </c>
-      <c r="F49" t="n">
+      <c r="F50" t="n">
         <v>1143</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="4" t="n">
+    <row r="51">
+      <c r="A51" s="4" t="n">
         <v>45689</v>
       </c>
-      <c r="B50" t="n">
+      <c r="B51" t="n">
         <v>28632</v>
       </c>
-      <c r="C50" t="n">
+      <c r="C51" t="n">
         <v>22088</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D51" t="n">
         <v>6544</v>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_feb25_ingles2.pdf</t>
         </is>
       </c>
-      <c r="F50" t="n">
+      <c r="F51" t="n">
         <v>1032</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="4" t="n">
+    <row r="52">
+      <c r="A52" s="4" t="n">
         <v>45717</v>
       </c>
-      <c r="B51" t="n">
+      <c r="B52" t="n">
         <v>28402</v>
       </c>
-      <c r="C51" t="n">
+      <c r="C52" t="n">
         <v>23054</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D52" t="n">
         <v>5348</v>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_mar25_ingles.pdf</t>
         </is>
       </c>
-      <c r="F51" t="n">
+      <c r="F52" t="n">
         <v>1094</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="4" t="n">
+    <row r="53">
+      <c r="A53" s="4" t="n">
         <v>45748</v>
       </c>
-      <c r="B52" t="n">
+      <c r="B53" t="n">
         <v>23090</v>
       </c>
-      <c r="C52" t="n">
+      <c r="C53" t="n">
         <v>17558</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D53" t="n">
         <v>5532</v>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_abr25_ingles.pdf</t>
         </is>
       </c>
-      <c r="F52" t="n">
+      <c r="F53" t="n">
         <v>928</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="4" t="n">
+    <row r="54">
+      <c r="A54" s="4" t="n">
         <v>45778</v>
       </c>
-      <c r="B53" t="n">
+      <c r="B54" t="n">
         <v>24446</v>
       </c>
-      <c r="C53" t="n">
+      <c r="C54" t="n">
         <v>17262</v>
       </c>
-      <c r="D53" t="n">
+      <c r="D54" t="n">
         <v>7185</v>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_may25_ingles_rev.pdf</t>
         </is>
       </c>
-      <c r="F53" t="n">
+      <c r="F54" t="n">
         <v>1005</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="4" t="n">
+    <row r="55">
+      <c r="A55" s="4" t="n">
         <v>45809</v>
       </c>
-      <c r="B54" t="n">
+      <c r="B55" t="n">
         <v>25548</v>
       </c>
-      <c r="C54" t="n">
+      <c r="C55" t="n">
         <v>15709</v>
       </c>
-      <c r="D54" t="n">
+      <c r="D55" t="n">
         <v>9839</v>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_jun25_ingles_rev.pdf</t>
         </is>
       </c>
-      <c r="F54" t="n">
+      <c r="F55" t="n">
         <v>935</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="4" t="n">
+    <row r="56">
+      <c r="A56" s="4" t="n">
         <v>45839</v>
       </c>
-      <c r="B55" t="n">
+      <c r="B56" t="n">
         <v>25378</v>
       </c>
-      <c r="C55" t="n">
+      <c r="C56" t="n">
         <v>16070</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D56" t="n">
         <v>9308</v>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E56" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_jul25_ingles_rev.pdf</t>
         </is>
       </c>
-      <c r="F55" t="n">
+      <c r="F56" t="n">
         <v>988</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="4" t="n">
+    <row r="57">
+      <c r="A57" s="4" t="n">
         <v>45870</v>
       </c>
-      <c r="B56" t="n">
+      <c r="B57" t="n">
         <v>22982</v>
       </c>
-      <c r="C56" t="n">
+      <c r="C57" t="n">
         <v>13857</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D57" t="n">
         <v>9125</v>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="E57" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_ago25_ingles_rev.pdf</t>
         </is>
       </c>
-      <c r="F56" t="n">
+      <c r="F57" t="n">
         <v>954</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="4" t="n">
+    <row r="58">
+      <c r="A58" s="4" t="n">
         <v>45901</v>
       </c>
-      <c r="B57" t="n">
+      <c r="B58" t="n">
         <v>24598</v>
       </c>
-      <c r="C57" t="n">
+      <c r="C58" t="n">
         <v>16139</v>
       </c>
-      <c r="D57" t="n">
+      <c r="D58" t="n">
         <v>8459</v>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_sep25_ingles.pdf</t>
         </is>
       </c>
-      <c r="F57" t="n">
+      <c r="F58" t="n">
         <v>1075</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="4" t="n">
+    <row r="59">
+      <c r="A59" s="4" t="n">
         <v>45931</v>
       </c>
-      <c r="B58" t="n">
+      <c r="B59" t="n">
         <v>29201</v>
       </c>
-      <c r="C58" t="n">
+      <c r="C59" t="n">
         <v>17887</v>
       </c>
-      <c r="D58" t="n">
+      <c r="D59" t="n">
         <v>11315</v>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="E59" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_oct25_ingles.pdf</t>
         </is>
       </c>
-      <c r="F58" t="n">
+      <c r="F59" t="n">
         <v>1107</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="4" t="n">
+    <row r="60">
+      <c r="A60" s="4" t="n">
         <v>45992</v>
       </c>
-      <c r="B59" t="n">
+      <c r="B60" t="n">
         <v>35236</v>
       </c>
-      <c r="C59" t="n">
+      <c r="C60" t="n">
         <v>24431</v>
       </c>
-      <c r="D59" t="n">
+      <c r="D60" t="n">
         <v>10805</v>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="E60" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_dic25_ingles.pdf</t>
         </is>
       </c>
-      <c r="F59" t="n">
+      <c r="F60" t="n">
         <v>1122</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="4" t="n">
+    <row r="61">
+      <c r="A61" s="4" t="n">
         <v>46023</v>
       </c>
-      <c r="B60" t="n">
+      <c r="B61" t="n">
         <v>36172</v>
       </c>
-      <c r="C60" t="n">
+      <c r="C61" t="n">
         <v>27138</v>
       </c>
-      <c r="D60" t="n">
+      <c r="D61" t="n">
         <v>9034</v>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_ene26_inglesrev.pdf</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="4" t="n">
+    <row r="62">
+      <c r="A62" s="4" t="n">
         <v>46054</v>
       </c>
-      <c r="B61" t="n">
+      <c r="B62" t="n">
         <v>27582</v>
       </c>
-      <c r="C61" t="n">
+      <c r="C62" t="n">
         <v>21088</v>
       </c>
-      <c r="D61" t="n">
+      <c r="D62" t="n">
         <v>6493</v>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_feb26_ingles_rev.pdf</t>
         </is>
       </c>
-      <c r="F61" t="n">
+      <c r="F62" t="n">
         <v>1059</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="4" t="n">
+    <row r="63">
+      <c r="A63" s="4" t="n">
         <v>46082</v>
       </c>
-      <c r="B62" t="n">
+      <c r="B63" t="n">
         <v>28765</v>
       </c>
-      <c r="C62" t="n">
+      <c r="C63" t="n">
         <v>20913</v>
       </c>
-      <c r="D62" t="n">
+      <c r="D63" t="n">
         <v>7852</v>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_mar26_ingles_rev.pdf</t>
         </is>
       </c>
-      <c r="F62" t="n">
+      <c r="F63" t="n">
         <v>1116</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="4" t="n">
+    <row r="64">
+      <c r="A64" s="4" t="n">
         <v>46113</v>
       </c>
-      <c r="B63" t="n">
+      <c r="B64" t="n">
         <v>23065</v>
       </c>
-      <c r="C63" t="n">
+      <c r="C64" t="n">
         <v>16448</v>
       </c>
-      <c r="D63" t="n">
+      <c r="D64" t="n">
         <v>6617</v>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_abr26_ingles.pdf</t>
         </is>
       </c>
-      <c r="F63" t="n">
+      <c r="F64" t="n">
         <v>952</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="4" t="n">
+    <row r="65">
+      <c r="A65" s="4" t="n">
         <v>46143</v>
       </c>
-      <c r="B64" t="n">
+      <c r="B65" t="n">
         <v>24196</v>
       </c>
-      <c r="C64" t="n">
+      <c r="C65" t="n">
         <v>16964</v>
       </c>
-      <c r="D64" t="n">
+      <c r="D65" t="n">
         <v>7232</v>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_may26_ingles.pdf</t>
         </is>
       </c>
-      <c r="F64" t="n">
+      <c r="F65" t="n">
         <v>957</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="4" t="n">
+    <row r="66">
+      <c r="A66" s="4" t="n">
         <v>46174</v>
       </c>
-      <c r="B65" t="n">
+      <c r="B66" t="n">
         <v>23840</v>
       </c>
-      <c r="C65" t="n">
+      <c r="C66" t="n">
         <v>15267</v>
       </c>
-      <c r="D65" t="n">
+      <c r="D66" t="n">
         <v>8573</v>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_jun26_ingles.pdf</t>
         </is>
       </c>
-      <c r="F65" t="n">
+      <c r="F66" t="n">
         <v>947</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="4" t="n">
+    <row r="67">
+      <c r="A67" s="4" t="n">
         <v>46204</v>
       </c>
-      <c r="B66" t="n">
+      <c r="B67" t="n">
         <v>27507</v>
       </c>
-      <c r="C66" t="n">
+      <c r="C67" t="n">
         <v>15263</v>
       </c>
-      <c r="D66" t="n">
+      <c r="D67" t="n">
         <v>12244</v>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_jul26_ingles_rev1.pdf</t>
         </is>
       </c>
-      <c r="F66" t="n">
+      <c r="F67" t="n">
         <v>1012</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="4" t="n">
+    <row r="68">
+      <c r="A68" s="4" t="n">
         <v>46235</v>
       </c>
-      <c r="B67" t="n">
+      <c r="B68" t="n">
         <v>25086</v>
       </c>
-      <c r="C67" t="n">
+      <c r="C68" t="n">
         <v>13134</v>
       </c>
-      <c r="D67" t="n">
+      <c r="D68" t="n">
         <v>11952</v>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_ago26_ingles.pdf</t>
         </is>
       </c>
-      <c r="F67" t="n">
+      <c r="F68" t="n">
         <v>948</v>
       </c>
     </row>

--- a/output/Data and Chart Outputs/europe_tso_gas_demand_extra_daily.xlsx
+++ b/output/Data and Chart Outputs/europe_tso_gas_demand_extra_daily.xlsx
@@ -819,7 +819,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-05 03:32 UTC; daily 2103 days 2021-01-01 to 2026-10-04; Spain monthly 67 months 2021-01 to 2026-08</t>
+          <t>2026-10-05 03:45 UTC; daily 2103 days 2021-01-01 to 2026-10-04; Spain monthly 67 months 2021-01 to 2026-08</t>
         </is>
       </c>
     </row>
@@ -86576,6 +86576,9 @@
           <t>Boletín%20Estadístico_febrero21_INGLES.pdf</t>
         </is>
       </c>
+      <c r="F3" t="n">
+        <v>1185</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n">
@@ -86595,6 +86598,9 @@
           <t>Boletín%20Estadístico_marzo21_INGLES_rev3.pdf</t>
         </is>
       </c>
+      <c r="F4" t="n">
+        <v>1184</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -86725,7 +86731,7 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1169</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="11">
@@ -86746,6 +86752,9 @@
           <t>Monthly-Bulletin-Gas-october-2021.pdf</t>
         </is>
       </c>
+      <c r="F11" t="n">
+        <v>1118</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
@@ -86787,6 +86796,9 @@
           <t>Monthly-Bulletin-Gas-december-2022.pdf</t>
         </is>
       </c>
+      <c r="F13" t="n">
+        <v>1305</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
@@ -86828,6 +86840,9 @@
           <t>Monthly-Bulletin-Gas-february-2022.pdf</t>
         </is>
       </c>
+      <c r="F15" t="n">
+        <v>1075</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
@@ -86847,6 +86862,9 @@
           <t>Monthly-Bulletin-Gas-march-2022.pdf</t>
         </is>
       </c>
+      <c r="F16" t="n">
+        <v>1311</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
@@ -86889,7 +86907,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>850</v>
+        <v>852</v>
       </c>
     </row>
     <row r="19">
@@ -86933,7 +86951,7 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1157</v>
+        <v>746</v>
       </c>
     </row>
     <row r="21">
@@ -86954,6 +86972,9 @@
           <t>Monthly-Bulletin-Gas-August-2022.pdf</t>
         </is>
       </c>
+      <c r="F21" t="n">
+        <v>734</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
@@ -86973,6 +86994,9 @@
           <t>Monthly-Bulletin-Gas-September-2022.pdf</t>
         </is>
       </c>
+      <c r="F22" t="n">
+        <v>732</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
@@ -86992,6 +87016,9 @@
           <t>Monthly-Bulletin-Gas-October-2022.pdf</t>
         </is>
       </c>
+      <c r="F23" t="n">
+        <v>782</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
@@ -87033,6 +87060,9 @@
           <t>Monthly-Bulletin-Gas-December-2022.pdf</t>
         </is>
       </c>
+      <c r="F25" t="n">
+        <v>859</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
@@ -87074,6 +87104,9 @@
           <t>Monthly-Bulletin-Gas-February-2023.pdf</t>
         </is>
       </c>
+      <c r="F27" t="n">
+        <v>980</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="n">
@@ -87093,6 +87126,9 @@
           <t>Monthly-Bulletin-Gas-March-2023.pdf</t>
         </is>
       </c>
+      <c r="F28" t="n">
+        <v>1143</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="n">
@@ -87112,6 +87148,9 @@
           <t>Monthly-Bulletin-Gas-April-2023.pdf</t>
         </is>
       </c>
+      <c r="F29" t="n">
+        <v>901</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="n">
@@ -87131,6 +87170,9 @@
           <t>Monthly%20Bulletin%20Gas%20May%202023.pdf</t>
         </is>
       </c>
+      <c r="F30" t="n">
+        <v>932</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="n">
@@ -87172,6 +87214,9 @@
           <t>Monthly%20Bulletin%20July23.pdf</t>
         </is>
       </c>
+      <c r="F32" t="n">
+        <v>902</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="n">
@@ -87191,6 +87236,9 @@
           <t>Monthly_bulletin_Aug23.pdf</t>
         </is>
       </c>
+      <c r="F33" t="n">
+        <v>896</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="n">
@@ -87210,6 +87258,9 @@
           <t>Monthly_bulletin_Sep23.pdf</t>
         </is>
       </c>
+      <c r="F34" t="n">
+        <v>923</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="n">
@@ -87229,6 +87280,9 @@
           <t>Monthly_bulletin_Oct23.pdf</t>
         </is>
       </c>
+      <c r="F35" t="n">
+        <v>950</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="n">
@@ -87271,7 +87325,7 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>1010</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="38">
@@ -87784,6 +87838,9 @@
           <t>Boletín%20Estadístico_ene26_inglesrev.pdf</t>
         </is>
       </c>
+      <c r="F61" t="n">
+        <v>1162</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="4" t="n">

--- a/output/Data and Chart Outputs/europe_tso_gas_demand_extra_daily.xlsx
+++ b/output/Data and Chart Outputs/europe_tso_gas_demand_extra_daily.xlsx
@@ -819,7 +819,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-05 03:45 UTC; daily 2103 days 2021-01-01 to 2026-10-04; Spain monthly 67 months 2021-01 to 2026-08</t>
+          <t>2026-10-05 03:48 UTC; daily 2103 days 2021-01-01 to 2026-10-04; Spain monthly 68 months 2021-01 to 2026-08</t>
         </is>
       </c>
     </row>
@@ -86501,7 +86501,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87800,199 +87800,207 @@
     </row>
     <row r="60">
       <c r="A60" s="4" t="n">
+        <v>45962</v>
+      </c>
+      <c r="F60" t="n">
+        <v>1078</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
         <v>45992</v>
       </c>
-      <c r="B60" t="n">
+      <c r="B61" t="n">
         <v>35236</v>
       </c>
-      <c r="C60" t="n">
+      <c r="C61" t="n">
         <v>24431</v>
       </c>
-      <c r="D60" t="n">
+      <c r="D61" t="n">
         <v>10805</v>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_dic25_ingles.pdf</t>
         </is>
       </c>
-      <c r="F60" t="n">
+      <c r="F61" t="n">
         <v>1122</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="4" t="n">
+    <row r="62">
+      <c r="A62" s="4" t="n">
         <v>46023</v>
       </c>
-      <c r="B61" t="n">
+      <c r="B62" t="n">
         <v>36172</v>
       </c>
-      <c r="C61" t="n">
+      <c r="C62" t="n">
         <v>27138</v>
       </c>
-      <c r="D61" t="n">
+      <c r="D62" t="n">
         <v>9034</v>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_ene26_inglesrev.pdf</t>
         </is>
       </c>
-      <c r="F61" t="n">
+      <c r="F62" t="n">
         <v>1162</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="4" t="n">
+    <row r="63">
+      <c r="A63" s="4" t="n">
         <v>46054</v>
       </c>
-      <c r="B62" t="n">
+      <c r="B63" t="n">
         <v>27582</v>
       </c>
-      <c r="C62" t="n">
+      <c r="C63" t="n">
         <v>21088</v>
       </c>
-      <c r="D62" t="n">
+      <c r="D63" t="n">
         <v>6493</v>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_feb26_ingles_rev.pdf</t>
         </is>
       </c>
-      <c r="F62" t="n">
+      <c r="F63" t="n">
         <v>1059</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="4" t="n">
+    <row r="64">
+      <c r="A64" s="4" t="n">
         <v>46082</v>
       </c>
-      <c r="B63" t="n">
+      <c r="B64" t="n">
         <v>28765</v>
       </c>
-      <c r="C63" t="n">
+      <c r="C64" t="n">
         <v>20913</v>
       </c>
-      <c r="D63" t="n">
+      <c r="D64" t="n">
         <v>7852</v>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_mar26_ingles_rev.pdf</t>
         </is>
       </c>
-      <c r="F63" t="n">
+      <c r="F64" t="n">
         <v>1116</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="4" t="n">
+    <row r="65">
+      <c r="A65" s="4" t="n">
         <v>46113</v>
       </c>
-      <c r="B64" t="n">
+      <c r="B65" t="n">
         <v>23065</v>
       </c>
-      <c r="C64" t="n">
+      <c r="C65" t="n">
         <v>16448</v>
       </c>
-      <c r="D64" t="n">
+      <c r="D65" t="n">
         <v>6617</v>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E65" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_abr26_ingles.pdf</t>
         </is>
       </c>
-      <c r="F64" t="n">
+      <c r="F65" t="n">
         <v>952</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="4" t="n">
+    <row r="66">
+      <c r="A66" s="4" t="n">
         <v>46143</v>
       </c>
-      <c r="B65" t="n">
+      <c r="B66" t="n">
         <v>24196</v>
       </c>
-      <c r="C65" t="n">
+      <c r="C66" t="n">
         <v>16964</v>
       </c>
-      <c r="D65" t="n">
+      <c r="D66" t="n">
         <v>7232</v>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E66" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_may26_ingles.pdf</t>
         </is>
       </c>
-      <c r="F65" t="n">
+      <c r="F66" t="n">
         <v>957</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="4" t="n">
+    <row r="67">
+      <c r="A67" s="4" t="n">
         <v>46174</v>
       </c>
-      <c r="B66" t="n">
+      <c r="B67" t="n">
         <v>23840</v>
       </c>
-      <c r="C66" t="n">
+      <c r="C67" t="n">
         <v>15267</v>
       </c>
-      <c r="D66" t="n">
+      <c r="D67" t="n">
         <v>8573</v>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E67" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_jun26_ingles.pdf</t>
         </is>
       </c>
-      <c r="F66" t="n">
+      <c r="F67" t="n">
         <v>947</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="4" t="n">
+    <row r="68">
+      <c r="A68" s="4" t="n">
         <v>46204</v>
       </c>
-      <c r="B67" t="n">
+      <c r="B68" t="n">
         <v>27507</v>
       </c>
-      <c r="C67" t="n">
+      <c r="C68" t="n">
         <v>15263</v>
       </c>
-      <c r="D67" t="n">
+      <c r="D68" t="n">
         <v>12244</v>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="E68" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_jul26_ingles_rev1.pdf</t>
         </is>
       </c>
-      <c r="F67" t="n">
+      <c r="F68" t="n">
         <v>1012</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="4" t="n">
+    <row r="69">
+      <c r="A69" s="4" t="n">
         <v>46235</v>
       </c>
-      <c r="B68" t="n">
+      <c r="B69" t="n">
         <v>25086</v>
       </c>
-      <c r="C68" t="n">
+      <c r="C69" t="n">
         <v>13134</v>
       </c>
-      <c r="D68" t="n">
+      <c r="D69" t="n">
         <v>11952</v>
       </c>
-      <c r="E68" t="inlineStr">
+      <c r="E69" t="inlineStr">
         <is>
           <t>Boletín%20Estadístico_ago26_ingles.pdf</t>
         </is>
       </c>
-      <c r="F68" t="n">
+      <c r="F69" t="n">
         <v>948</v>
       </c>
     </row>

--- a/output/Data and Chart Outputs/europe_tso_gas_demand_extra_daily.xlsx
+++ b/output/Data and Chart Outputs/europe_tso_gas_demand_extra_daily.xlsx
@@ -156,6 +156,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Gas consumption: Poland, Romania, Finland, Spain (operator data) (to Sep/26)</a:t>
             </a:r>
           </a:p>
@@ -819,7 +820,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-05 03:48 UTC; daily 2103 days 2021-01-01 to 2026-10-04; Spain monthly 68 months 2021-01 to 2026-08</t>
+          <t>2026-10-08 08:16 UTC; daily 2107 days 2021-01-01 to 2026-10-08; Spain monthly 68 months 2021-01 to 2026-08</t>
         </is>
       </c>
     </row>
@@ -2210,13 +2211,16 @@
         <v>46266</v>
       </c>
       <c r="B70" t="n">
-        <v>11.56258</v>
+        <v>11.56477</v>
       </c>
       <c r="C70" t="n">
         <v>4.375109999999999</v>
       </c>
+      <c r="D70" t="n">
+        <v>0.4797</v>
+      </c>
       <c r="E70" t="n">
-        <v>1.1415</v>
+        <v>1.14147</v>
       </c>
     </row>
   </sheetData>
@@ -2231,7 +2235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2104"/>
+  <dimension ref="A1:M2108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85227,19 +85231,19 @@
         <v>46266</v>
       </c>
       <c r="B2071" t="n">
-        <v>251.95</v>
+        <v>252.35</v>
       </c>
       <c r="C2071" t="n">
-        <v>115.79</v>
+        <v>115.78</v>
       </c>
       <c r="D2071" t="n">
         <v>0.74</v>
       </c>
       <c r="E2071" t="n">
-        <v>368.48</v>
+        <v>368.87</v>
       </c>
       <c r="F2071" t="n">
-        <v>5.45</v>
+        <v>5.46</v>
       </c>
       <c r="G2071" t="n">
         <v>71.31999999999999</v>
@@ -85258,6 +85262,9 @@
       </c>
       <c r="L2071" t="n">
         <v>37.11</v>
+      </c>
+      <c r="M2071" t="n">
+        <v>14.1</v>
       </c>
     </row>
     <row r="2072">
@@ -85265,7 +85272,7 @@
         <v>46267</v>
       </c>
       <c r="B2072" t="n">
-        <v>256.31</v>
+        <v>256.72</v>
       </c>
       <c r="C2072" t="n">
         <v>120.23</v>
@@ -85274,10 +85281,10 @@
         <v>0.61</v>
       </c>
       <c r="E2072" t="n">
-        <v>377.14</v>
+        <v>377.56</v>
       </c>
       <c r="F2072" t="n">
-        <v>5.39</v>
+        <v>5.4</v>
       </c>
       <c r="G2072" t="n">
         <v>72.15000000000001</v>
@@ -85296,6 +85303,9 @@
       </c>
       <c r="L2072" t="n">
         <v>37.18</v>
+      </c>
+      <c r="M2072" t="n">
+        <v>16.3</v>
       </c>
     </row>
     <row r="2073">
@@ -85303,19 +85313,19 @@
         <v>46268</v>
       </c>
       <c r="B2073" t="n">
-        <v>259.94</v>
+        <v>260.12</v>
       </c>
       <c r="C2073" t="n">
-        <v>109.2</v>
+        <v>109.19</v>
       </c>
       <c r="D2073" t="n">
         <v>0.98</v>
       </c>
       <c r="E2073" t="n">
-        <v>370.12</v>
+        <v>370.29</v>
       </c>
       <c r="F2073" t="n">
-        <v>5.44</v>
+        <v>5.45</v>
       </c>
       <c r="G2073" t="n">
         <v>72.79000000000001</v>
@@ -85334,6 +85344,9 @@
       </c>
       <c r="L2073" t="n">
         <v>37.01</v>
+      </c>
+      <c r="M2073" t="n">
+        <v>14.6</v>
       </c>
     </row>
     <row r="2074">
@@ -85341,10 +85354,10 @@
         <v>46269</v>
       </c>
       <c r="B2074" t="n">
-        <v>252.69</v>
+        <v>252.7</v>
       </c>
       <c r="C2074" t="n">
-        <v>85.81</v>
+        <v>85.8</v>
       </c>
       <c r="D2074" t="n">
         <v>0.93</v>
@@ -85353,7 +85366,7 @@
         <v>339.44</v>
       </c>
       <c r="F2074" t="n">
-        <v>5.7</v>
+        <v>5.71</v>
       </c>
       <c r="G2074" t="n">
         <v>68.70999999999999</v>
@@ -85372,6 +85385,9 @@
       </c>
       <c r="L2074" t="n">
         <v>36.62</v>
+      </c>
+      <c r="M2074" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="2075">
@@ -85379,16 +85395,16 @@
         <v>46270</v>
       </c>
       <c r="B2075" t="n">
-        <v>231.14</v>
+        <v>231.15</v>
       </c>
       <c r="C2075" t="n">
-        <v>79.45999999999999</v>
+        <v>79.45</v>
       </c>
       <c r="D2075" t="n">
         <v>1.37</v>
       </c>
       <c r="E2075" t="n">
-        <v>311.97</v>
+        <v>311.96</v>
       </c>
       <c r="F2075" t="n">
         <v>5.64</v>
@@ -85410,6 +85426,9 @@
       </c>
       <c r="L2075" t="n">
         <v>33.43</v>
+      </c>
+      <c r="M2075" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="2076">
@@ -85417,19 +85436,19 @@
         <v>46271</v>
       </c>
       <c r="B2076" t="n">
-        <v>237.18</v>
+        <v>237.17</v>
       </c>
       <c r="C2076" t="n">
-        <v>90.69</v>
+        <v>90.68000000000001</v>
       </c>
       <c r="D2076" t="n">
         <v>1.54</v>
       </c>
       <c r="E2076" t="n">
-        <v>329.41</v>
+        <v>329.39</v>
       </c>
       <c r="F2076" t="n">
-        <v>5.07</v>
+        <v>5.08</v>
       </c>
       <c r="G2076" t="n">
         <v>57.89</v>
@@ -85448,6 +85467,9 @@
       </c>
       <c r="L2076" t="n">
         <v>32.81</v>
+      </c>
+      <c r="M2076" t="n">
+        <v>14.2</v>
       </c>
     </row>
     <row r="2077">
@@ -85455,19 +85477,19 @@
         <v>46272</v>
       </c>
       <c r="B2077" t="n">
-        <v>260.03</v>
+        <v>260.07</v>
       </c>
       <c r="C2077" t="n">
-        <v>101.87</v>
+        <v>101.86</v>
       </c>
       <c r="D2077" t="n">
         <v>0.83</v>
       </c>
       <c r="E2077" t="n">
-        <v>362.73</v>
+        <v>362.76</v>
       </c>
       <c r="F2077" t="n">
-        <v>5.25</v>
+        <v>5.26</v>
       </c>
       <c r="G2077" t="n">
         <v>73.47</v>
@@ -85486,6 +85508,9 @@
       </c>
       <c r="L2077" t="n">
         <v>37.07</v>
+      </c>
+      <c r="M2077" t="n">
+        <v>13.3</v>
       </c>
     </row>
     <row r="2078">
@@ -85493,19 +85518,19 @@
         <v>46273</v>
       </c>
       <c r="B2078" t="n">
-        <v>261.2</v>
+        <v>261.29</v>
       </c>
       <c r="C2078" t="n">
-        <v>101.66</v>
+        <v>101.61</v>
       </c>
       <c r="D2078" t="n">
         <v>0.79</v>
       </c>
       <c r="E2078" t="n">
-        <v>363.65</v>
+        <v>363.69</v>
       </c>
       <c r="F2078" t="n">
-        <v>5.98</v>
+        <v>5.99</v>
       </c>
       <c r="G2078" t="n">
         <v>72.51000000000001</v>
@@ -85524,6 +85549,9 @@
       </c>
       <c r="L2078" t="n">
         <v>37.59</v>
+      </c>
+      <c r="M2078" t="n">
+        <v>13.8</v>
       </c>
     </row>
     <row r="2079">
@@ -85531,16 +85559,16 @@
         <v>46274</v>
       </c>
       <c r="B2079" t="n">
-        <v>255.49</v>
+        <v>255.64</v>
       </c>
       <c r="C2079" t="n">
-        <v>108.1</v>
+        <v>108.09</v>
       </c>
       <c r="D2079" t="n">
         <v>0.38</v>
       </c>
       <c r="E2079" t="n">
-        <v>363.97</v>
+        <v>364.11</v>
       </c>
       <c r="F2079" t="n">
         <v>6.01</v>
@@ -85558,10 +85586,13 @@
         <v>13.74</v>
       </c>
       <c r="K2079" t="n">
-        <v>23.66</v>
+        <v>23.65</v>
       </c>
       <c r="L2079" t="n">
         <v>37.39</v>
+      </c>
+      <c r="M2079" t="n">
+        <v>16.7</v>
       </c>
     </row>
     <row r="2080">
@@ -85569,16 +85600,16 @@
         <v>46275</v>
       </c>
       <c r="B2080" t="n">
-        <v>266.02</v>
+        <v>263.51</v>
       </c>
       <c r="C2080" t="n">
-        <v>118.45</v>
+        <v>118.44</v>
       </c>
       <c r="D2080" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="E2080" t="n">
-        <v>385.41</v>
+        <v>382.88</v>
       </c>
       <c r="F2080" t="n">
         <v>6.79</v>
@@ -85600,6 +85631,9 @@
       </c>
       <c r="L2080" t="n">
         <v>38.37</v>
+      </c>
+      <c r="M2080" t="n">
+        <v>14.9</v>
       </c>
     </row>
     <row r="2081">
@@ -85607,7 +85641,7 @@
         <v>46276</v>
       </c>
       <c r="B2081" t="n">
-        <v>268.37</v>
+        <v>268.33</v>
       </c>
       <c r="C2081" t="n">
         <v>133.51</v>
@@ -85616,10 +85650,10 @@
         <v>0.88</v>
       </c>
       <c r="E2081" t="n">
-        <v>402.77</v>
+        <v>402.72</v>
       </c>
       <c r="F2081" t="n">
-        <v>6.65</v>
+        <v>6.67</v>
       </c>
       <c r="G2081" t="n">
         <v>74.3</v>
@@ -85638,6 +85672,9 @@
       </c>
       <c r="L2081" t="n">
         <v>37.84</v>
+      </c>
+      <c r="M2081" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="2082">
@@ -85645,16 +85682,16 @@
         <v>46277</v>
       </c>
       <c r="B2082" t="n">
-        <v>243.74</v>
+        <v>243.82</v>
       </c>
       <c r="C2082" t="n">
-        <v>91.42</v>
+        <v>91.41</v>
       </c>
       <c r="D2082" t="n">
         <v>1.3</v>
       </c>
       <c r="E2082" t="n">
-        <v>336.46</v>
+        <v>336.52</v>
       </c>
       <c r="F2082" t="n">
         <v>5.94</v>
@@ -85676,6 +85713,9 @@
       </c>
       <c r="L2082" t="n">
         <v>34.91</v>
+      </c>
+      <c r="M2082" t="n">
+        <v>14.6</v>
       </c>
     </row>
     <row r="2083">
@@ -85683,19 +85723,19 @@
         <v>46278</v>
       </c>
       <c r="B2083" t="n">
-        <v>239.28</v>
+        <v>239.33</v>
       </c>
       <c r="C2083" t="n">
-        <v>97.76000000000001</v>
+        <v>97.75</v>
       </c>
       <c r="D2083" t="n">
         <v>1.16</v>
       </c>
       <c r="E2083" t="n">
-        <v>338.2</v>
+        <v>338.24</v>
       </c>
       <c r="F2083" t="n">
-        <v>5.06</v>
+        <v>5.07</v>
       </c>
       <c r="G2083" t="n">
         <v>70.95</v>
@@ -85714,6 +85754,9 @@
       </c>
       <c r="L2083" t="n">
         <v>34.85</v>
+      </c>
+      <c r="M2083" t="n">
+        <v>14.8</v>
       </c>
     </row>
     <row r="2084">
@@ -85721,19 +85764,19 @@
         <v>46279</v>
       </c>
       <c r="B2084" t="n">
-        <v>266.67</v>
+        <v>266.85</v>
       </c>
       <c r="C2084" t="n">
-        <v>118.67</v>
+        <v>118.76</v>
       </c>
       <c r="D2084" t="n">
         <v>0.91</v>
       </c>
       <c r="E2084" t="n">
-        <v>386.24</v>
+        <v>386.52</v>
       </c>
       <c r="F2084" t="n">
-        <v>5.54</v>
+        <v>5.55</v>
       </c>
       <c r="G2084" t="n">
         <v>75.59</v>
@@ -85752,6 +85795,9 @@
       </c>
       <c r="L2084" t="n">
         <v>39.61</v>
+      </c>
+      <c r="M2084" t="n">
+        <v>21.6</v>
       </c>
     </row>
     <row r="2085">
@@ -85759,7 +85805,7 @@
         <v>46280</v>
       </c>
       <c r="B2085" t="n">
-        <v>272.73</v>
+        <v>272.92</v>
       </c>
       <c r="C2085" t="n">
         <v>111.37</v>
@@ -85768,10 +85814,10 @@
         <v>1.2</v>
       </c>
       <c r="E2085" t="n">
-        <v>385.3</v>
+        <v>385.49</v>
       </c>
       <c r="F2085" t="n">
-        <v>6.24</v>
+        <v>6.25</v>
       </c>
       <c r="G2085" t="n">
         <v>75.27</v>
@@ -85790,6 +85836,9 @@
       </c>
       <c r="L2085" t="n">
         <v>39.85</v>
+      </c>
+      <c r="M2085" t="n">
+        <v>17.3</v>
       </c>
     </row>
     <row r="2086">
@@ -85797,19 +85846,19 @@
         <v>46281</v>
       </c>
       <c r="B2086" t="n">
-        <v>266.29</v>
+        <v>266.56</v>
       </c>
       <c r="C2086" t="n">
-        <v>121.13</v>
+        <v>121.12</v>
       </c>
       <c r="D2086" t="n">
         <v>0.33</v>
       </c>
       <c r="E2086" t="n">
-        <v>387.75</v>
+        <v>388.01</v>
       </c>
       <c r="F2086" t="n">
-        <v>6.12</v>
+        <v>6.13</v>
       </c>
       <c r="G2086" t="n">
         <v>76.16</v>
@@ -85828,6 +85877,9 @@
       </c>
       <c r="L2086" t="n">
         <v>40.02</v>
+      </c>
+      <c r="M2086" t="n">
+        <v>15.6</v>
       </c>
     </row>
     <row r="2087">
@@ -85835,19 +85887,19 @@
         <v>46282</v>
       </c>
       <c r="B2087" t="n">
-        <v>270.73</v>
+        <v>271.2</v>
       </c>
       <c r="C2087" t="n">
-        <v>131.09</v>
+        <v>131.08</v>
       </c>
       <c r="D2087" t="n">
         <v>0.6899999999999999</v>
       </c>
       <c r="E2087" t="n">
-        <v>402.51</v>
+        <v>402.98</v>
       </c>
       <c r="F2087" t="n">
-        <v>5.64</v>
+        <v>5.65</v>
       </c>
       <c r="G2087" t="n">
         <v>75.09</v>
@@ -85866,6 +85918,9 @@
       </c>
       <c r="L2087" t="n">
         <v>42.25</v>
+      </c>
+      <c r="M2087" t="n">
+        <v>14.6</v>
       </c>
     </row>
     <row r="2088">
@@ -85873,19 +85928,19 @@
         <v>46283</v>
       </c>
       <c r="B2088" t="n">
-        <v>265.45</v>
+        <v>265.69</v>
       </c>
       <c r="C2088" t="n">
-        <v>113.8</v>
+        <v>113.79</v>
       </c>
       <c r="D2088" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="E2088" t="n">
-        <v>379.8</v>
+        <v>380.04</v>
       </c>
       <c r="F2088" t="n">
-        <v>5.36</v>
+        <v>5.37</v>
       </c>
       <c r="G2088" t="n">
         <v>73.73</v>
@@ -85904,6 +85959,9 @@
       </c>
       <c r="L2088" t="n">
         <v>37.83</v>
+      </c>
+      <c r="M2088" t="n">
+        <v>13.5</v>
       </c>
     </row>
     <row r="2089">
@@ -85911,19 +85969,19 @@
         <v>46284</v>
       </c>
       <c r="B2089" t="n">
-        <v>241.16</v>
+        <v>241.37</v>
       </c>
       <c r="C2089" t="n">
-        <v>95.81999999999999</v>
+        <v>95.81</v>
       </c>
       <c r="D2089" t="n">
         <v>1.03</v>
       </c>
       <c r="E2089" t="n">
-        <v>338.02</v>
+        <v>338.21</v>
       </c>
       <c r="F2089" t="n">
-        <v>5.44</v>
+        <v>5.45</v>
       </c>
       <c r="G2089" t="n">
         <v>69.56999999999999</v>
@@ -85941,7 +85999,10 @@
         <v>15.67</v>
       </c>
       <c r="L2089" t="n">
-        <v>27.36</v>
+        <v>27.35</v>
+      </c>
+      <c r="M2089" t="n">
+        <v>12.8</v>
       </c>
     </row>
     <row r="2090">
@@ -85949,19 +86010,19 @@
         <v>46285</v>
       </c>
       <c r="B2090" t="n">
-        <v>242.21</v>
+        <v>242.44</v>
       </c>
       <c r="C2090" t="n">
-        <v>87.36</v>
+        <v>87.37</v>
       </c>
       <c r="D2090" t="n">
         <v>1.28</v>
       </c>
       <c r="E2090" t="n">
-        <v>330.85</v>
+        <v>331.09</v>
       </c>
       <c r="F2090" t="n">
-        <v>5.68</v>
+        <v>5.69</v>
       </c>
       <c r="G2090" t="n">
         <v>67.25</v>
@@ -85980,6 +86041,9 @@
       </c>
       <c r="L2090" t="n">
         <v>25.39</v>
+      </c>
+      <c r="M2090" t="n">
+        <v>14.1</v>
       </c>
     </row>
     <row r="2091">
@@ -85987,7 +86051,7 @@
         <v>46286</v>
       </c>
       <c r="B2091" t="n">
-        <v>285.47</v>
+        <v>285.76</v>
       </c>
       <c r="C2091" t="n">
         <v>107.52</v>
@@ -85996,10 +86060,10 @@
         <v>0.44</v>
       </c>
       <c r="E2091" t="n">
-        <v>393.43</v>
+        <v>393.72</v>
       </c>
       <c r="F2091" t="n">
-        <v>5.94</v>
+        <v>5.96</v>
       </c>
       <c r="G2091" t="n">
         <v>73.76000000000001</v>
@@ -86018,6 +86082,9 @@
       </c>
       <c r="L2091" t="n">
         <v>30.37</v>
+      </c>
+      <c r="M2091" t="n">
+        <v>19.1</v>
       </c>
     </row>
     <row r="2092">
@@ -86025,7 +86092,7 @@
         <v>46287</v>
       </c>
       <c r="B2092" t="n">
-        <v>300.78</v>
+        <v>301.09</v>
       </c>
       <c r="C2092" t="n">
         <v>141.93</v>
@@ -86034,10 +86101,10 @@
         <v>0.36</v>
       </c>
       <c r="E2092" t="n">
-        <v>443.07</v>
+        <v>443.38</v>
       </c>
       <c r="F2092" t="n">
-        <v>6.79</v>
+        <v>6.8</v>
       </c>
       <c r="G2092" t="n">
         <v>76.5</v>
@@ -86055,7 +86122,10 @@
         <v>19.94</v>
       </c>
       <c r="L2092" t="n">
-        <v>38.16</v>
+        <v>38.15</v>
+      </c>
+      <c r="M2092" t="n">
+        <v>18.9</v>
       </c>
     </row>
     <row r="2093">
@@ -86063,19 +86133,19 @@
         <v>46288</v>
       </c>
       <c r="B2093" t="n">
-        <v>309.06</v>
+        <v>309.38</v>
       </c>
       <c r="C2093" t="n">
-        <v>142.28</v>
+        <v>142.27</v>
       </c>
       <c r="D2093" t="n">
         <v>0.08</v>
       </c>
       <c r="E2093" t="n">
-        <v>451.42</v>
+        <v>451.73</v>
       </c>
       <c r="F2093" t="n">
-        <v>7.95</v>
+        <v>7.97</v>
       </c>
       <c r="G2093" t="n">
         <v>77.75</v>
@@ -86094,6 +86164,9 @@
       </c>
       <c r="L2093" t="n">
         <v>44.55</v>
+      </c>
+      <c r="M2093" t="n">
+        <v>18.2</v>
       </c>
     </row>
     <row r="2094">
@@ -86101,19 +86174,19 @@
         <v>46289</v>
       </c>
       <c r="B2094" t="n">
-        <v>319.42</v>
+        <v>319.73</v>
       </c>
       <c r="C2094" t="n">
-        <v>147.88</v>
+        <v>147.87</v>
       </c>
       <c r="D2094" t="n">
         <v>0.16</v>
       </c>
       <c r="E2094" t="n">
-        <v>467.47</v>
+        <v>467.77</v>
       </c>
       <c r="F2094" t="n">
-        <v>7.35</v>
+        <v>7.37</v>
       </c>
       <c r="G2094" t="n">
         <v>78.44</v>
@@ -86131,7 +86204,10 @@
         <v>25.3</v>
       </c>
       <c r="L2094" t="n">
-        <v>45.37</v>
+        <v>45.36</v>
+      </c>
+      <c r="M2094" t="n">
+        <v>19.2</v>
       </c>
     </row>
     <row r="2095">
@@ -86139,7 +86215,7 @@
         <v>46290</v>
       </c>
       <c r="B2095" t="n">
-        <v>320.56</v>
+        <v>320.72</v>
       </c>
       <c r="C2095" t="n">
         <v>153.03</v>
@@ -86148,7 +86224,7 @@
         <v>1.14</v>
       </c>
       <c r="E2095" t="n">
-        <v>474.73</v>
+        <v>474.89</v>
       </c>
       <c r="F2095" t="n">
         <v>7.14</v>
@@ -86166,10 +86242,13 @@
         <v>19.8</v>
       </c>
       <c r="K2095" t="n">
-        <v>25.06</v>
+        <v>25.07</v>
       </c>
       <c r="L2095" t="n">
-        <v>44.86</v>
+        <v>44.87</v>
+      </c>
+      <c r="M2095" t="n">
+        <v>16.1</v>
       </c>
     </row>
     <row r="2096">
@@ -86177,16 +86256,16 @@
         <v>46291</v>
       </c>
       <c r="B2096" t="n">
-        <v>286.88</v>
+        <v>286.94</v>
       </c>
       <c r="C2096" t="n">
-        <v>123.38</v>
+        <v>123.37</v>
       </c>
       <c r="D2096" t="n">
         <v>1.84</v>
       </c>
       <c r="E2096" t="n">
-        <v>412.1</v>
+        <v>412.15</v>
       </c>
       <c r="F2096" t="n">
         <v>7.46</v>
@@ -86208,6 +86287,9 @@
       </c>
       <c r="L2096" t="n">
         <v>41.44</v>
+      </c>
+      <c r="M2096" t="n">
+        <v>18.2</v>
       </c>
     </row>
     <row r="2097">
@@ -86215,16 +86297,16 @@
         <v>46292</v>
       </c>
       <c r="B2097" t="n">
-        <v>273.39</v>
+        <v>273.44</v>
       </c>
       <c r="C2097" t="n">
-        <v>115.5</v>
+        <v>115.49</v>
       </c>
       <c r="D2097" t="n">
         <v>1.63</v>
       </c>
       <c r="E2097" t="n">
-        <v>390.52</v>
+        <v>390.56</v>
       </c>
       <c r="F2097" t="n">
         <v>6.73</v>
@@ -86246,6 +86328,9 @@
       </c>
       <c r="L2097" t="n">
         <v>40.31</v>
+      </c>
+      <c r="M2097" t="n">
+        <v>17.8</v>
       </c>
     </row>
     <row r="2098">
@@ -86253,16 +86338,16 @@
         <v>46293</v>
       </c>
       <c r="B2098" t="n">
-        <v>294.57</v>
+        <v>294.64</v>
       </c>
       <c r="C2098" t="n">
-        <v>133.28</v>
+        <v>133.31</v>
       </c>
       <c r="D2098" t="n">
         <v>1.8</v>
       </c>
       <c r="E2098" t="n">
-        <v>429.65</v>
+        <v>429.75</v>
       </c>
       <c r="F2098" t="n">
         <v>6.94</v>
@@ -86283,7 +86368,10 @@
         <v>24.68</v>
       </c>
       <c r="L2098" t="n">
-        <v>43.91</v>
+        <v>43.9</v>
+      </c>
+      <c r="M2098" t="n">
+        <v>17.9</v>
       </c>
     </row>
     <row r="2099">
@@ -86291,10 +86379,10 @@
         <v>46294</v>
       </c>
       <c r="B2099" t="n">
-        <v>299.47</v>
+        <v>299.48</v>
       </c>
       <c r="C2099" t="n">
-        <v>123.35</v>
+        <v>123.34</v>
       </c>
       <c r="D2099" t="n">
         <v>1.9</v>
@@ -86322,6 +86410,9 @@
       </c>
       <c r="L2099" t="n">
         <v>44.38</v>
+      </c>
+      <c r="M2099" t="n">
+        <v>18.5</v>
       </c>
     </row>
     <row r="2100">
@@ -86329,16 +86420,16 @@
         <v>46295</v>
       </c>
       <c r="B2100" t="n">
-        <v>293.45</v>
+        <v>293.55</v>
       </c>
       <c r="C2100" t="n">
-        <v>119.59</v>
+        <v>119.58</v>
       </c>
       <c r="D2100" t="n">
         <v>2.21</v>
       </c>
       <c r="E2100" t="n">
-        <v>415.25</v>
+        <v>415.33</v>
       </c>
       <c r="F2100" t="n">
         <v>7.22</v>
@@ -86360,6 +86451,9 @@
       </c>
       <c r="L2100" t="n">
         <v>43.66</v>
+      </c>
+      <c r="M2100" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="2101">
@@ -86480,14 +86574,157 @@
       <c r="A2104" s="4" t="n">
         <v>46299</v>
       </c>
+      <c r="B2104" t="n">
+        <v>273.23</v>
+      </c>
+      <c r="C2104" t="n">
+        <v>107.1</v>
+      </c>
+      <c r="D2104" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="E2104" t="n">
+        <v>382.15</v>
+      </c>
+      <c r="F2104" t="n">
+        <v>6.28</v>
+      </c>
+      <c r="G2104" t="n">
+        <v>55.96</v>
+      </c>
+      <c r="H2104" t="n">
+        <v>93.48999999999999</v>
+      </c>
+      <c r="I2104" t="n">
+        <v>149.45</v>
+      </c>
       <c r="J2104" t="n">
-        <v>8.779999999999999</v>
+        <v>17.05</v>
       </c>
       <c r="K2104" t="n">
-        <v>11.73</v>
+        <v>24.27</v>
       </c>
       <c r="L2104" t="n">
-        <v>20.51</v>
+        <v>41.32</v>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B2105" t="n">
+        <v>304.53</v>
+      </c>
+      <c r="C2105" t="n">
+        <v>121.83</v>
+      </c>
+      <c r="D2105" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="E2105" t="n">
+        <v>428.2</v>
+      </c>
+      <c r="F2105" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="G2105" t="n">
+        <v>63.85</v>
+      </c>
+      <c r="H2105" t="n">
+        <v>111.68</v>
+      </c>
+      <c r="I2105" t="n">
+        <v>175.53</v>
+      </c>
+      <c r="J2105" t="n">
+        <v>22.31</v>
+      </c>
+      <c r="K2105" t="n">
+        <v>24.94</v>
+      </c>
+      <c r="L2105" t="n">
+        <v>47.25</v>
+      </c>
+    </row>
+    <row r="2106">
+      <c r="A2106" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B2106" t="n">
+        <v>304.85</v>
+      </c>
+      <c r="C2106" t="n">
+        <v>138.66</v>
+      </c>
+      <c r="D2106" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="E2106" t="n">
+        <v>445.68</v>
+      </c>
+      <c r="F2106" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="G2106" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="H2106" t="n">
+        <v>108.73</v>
+      </c>
+      <c r="I2106" t="n">
+        <v>175.03</v>
+      </c>
+      <c r="J2106" t="n">
+        <v>23.16</v>
+      </c>
+      <c r="K2106" t="n">
+        <v>25.01</v>
+      </c>
+      <c r="L2106" t="n">
+        <v>48.17</v>
+      </c>
+    </row>
+    <row r="2107">
+      <c r="A2107" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B2107" t="n">
+        <v>303.15</v>
+      </c>
+      <c r="C2107" t="n">
+        <v>119.93</v>
+      </c>
+      <c r="D2107" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E2107" t="n">
+        <v>424.58</v>
+      </c>
+      <c r="F2107" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="J2107" t="n">
+        <v>21.21</v>
+      </c>
+      <c r="K2107" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="L2107" t="n">
+        <v>45.71</v>
+      </c>
+    </row>
+    <row r="2108">
+      <c r="A2108" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="J2108" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2108" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2108" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/europe_tso_gas_demand_extra_daily.xlsx
+++ b/output/Data and Chart Outputs/europe_tso_gas_demand_extra_daily.xlsx
@@ -820,7 +820,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-08 08:16 UTC; daily 2107 days 2021-01-01 to 2026-10-08; Spain monthly 68 months 2021-01 to 2026-08</t>
+          <t>2026-10-28 00:45 UTC; daily 2126 days 2021-01-01 to 2026-10-27; Spain monthly 69 months 2021-01 to 2026-09</t>
         </is>
       </c>
     </row>
@@ -2220,7 +2220,10 @@
         <v>0.4797</v>
       </c>
       <c r="E70" t="n">
-        <v>1.14147</v>
+        <v>1.14164</v>
+      </c>
+      <c r="F70" t="n">
+        <v>25.817</v>
       </c>
     </row>
   </sheetData>
@@ -2235,7 +2238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M2108"/>
+  <dimension ref="A1:M2127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85255,7 +85258,7 @@
         <v>136.01</v>
       </c>
       <c r="J2071" t="n">
-        <v>13.24</v>
+        <v>13.25</v>
       </c>
       <c r="K2071" t="n">
         <v>23.86</v>
@@ -85501,13 +85504,13 @@
         <v>140.6</v>
       </c>
       <c r="J2077" t="n">
-        <v>12.97</v>
+        <v>12.98</v>
       </c>
       <c r="K2077" t="n">
         <v>24.1</v>
       </c>
       <c r="L2077" t="n">
-        <v>37.07</v>
+        <v>37.08</v>
       </c>
       <c r="M2077" t="n">
         <v>13.3</v>
@@ -85542,13 +85545,13 @@
         <v>138.98</v>
       </c>
       <c r="J2078" t="n">
-        <v>13.63</v>
+        <v>13.64</v>
       </c>
       <c r="K2078" t="n">
         <v>23.96</v>
       </c>
       <c r="L2078" t="n">
-        <v>37.59</v>
+        <v>37.6</v>
       </c>
       <c r="M2078" t="n">
         <v>13.8</v>
@@ -85665,13 +85668,13 @@
         <v>142.62</v>
       </c>
       <c r="J2081" t="n">
-        <v>14.41</v>
+        <v>14.49</v>
       </c>
       <c r="K2081" t="n">
         <v>23.43</v>
       </c>
       <c r="L2081" t="n">
-        <v>37.84</v>
+        <v>37.92</v>
       </c>
       <c r="M2081" t="n">
         <v>15</v>
@@ -85706,13 +85709,13 @@
         <v>134.21</v>
       </c>
       <c r="J2082" t="n">
-        <v>11.52</v>
+        <v>11.57</v>
       </c>
       <c r="K2082" t="n">
         <v>23.39</v>
       </c>
       <c r="L2082" t="n">
-        <v>34.91</v>
+        <v>34.96</v>
       </c>
       <c r="M2082" t="n">
         <v>14.6</v>
@@ -85747,13 +85750,13 @@
         <v>135.2</v>
       </c>
       <c r="J2083" t="n">
-        <v>10.96</v>
+        <v>10.97</v>
       </c>
       <c r="K2083" t="n">
         <v>23.89</v>
       </c>
       <c r="L2083" t="n">
-        <v>34.85</v>
+        <v>34.86</v>
       </c>
       <c r="M2083" t="n">
         <v>14.8</v>
@@ -85999,7 +86002,7 @@
         <v>15.67</v>
       </c>
       <c r="L2089" t="n">
-        <v>27.35</v>
+        <v>27.36</v>
       </c>
       <c r="M2089" t="n">
         <v>12.8</v>
@@ -86502,7 +86505,7 @@
         <v>294.52</v>
       </c>
       <c r="C2102" t="n">
-        <v>123.27</v>
+        <v>123.28</v>
       </c>
       <c r="D2102" t="n">
         <v>1.86</v>
@@ -86703,6 +86706,15 @@
       <c r="F2107" t="n">
         <v>8.08</v>
       </c>
+      <c r="G2107" t="n">
+        <v>66.04000000000001</v>
+      </c>
+      <c r="H2107" t="n">
+        <v>106.34</v>
+      </c>
+      <c r="I2107" t="n">
+        <v>172.39</v>
+      </c>
       <c r="J2107" t="n">
         <v>21.21</v>
       </c>
@@ -86717,14 +86729,736 @@
       <c r="A2108" s="4" t="n">
         <v>46303</v>
       </c>
+      <c r="B2108" t="n">
+        <v>305.82</v>
+      </c>
+      <c r="C2108" t="n">
+        <v>118.45</v>
+      </c>
+      <c r="D2108" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="E2108" t="n">
+        <v>425.38</v>
+      </c>
+      <c r="F2108" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="G2108" t="n">
+        <v>64.05</v>
+      </c>
+      <c r="H2108" t="n">
+        <v>102.39</v>
+      </c>
+      <c r="I2108" t="n">
+        <v>166.44</v>
+      </c>
       <c r="J2108" t="n">
-        <v>0</v>
+        <v>19.85</v>
       </c>
       <c r="K2108" t="n">
-        <v>0</v>
+        <v>24.96</v>
       </c>
       <c r="L2108" t="n">
-        <v>0</v>
+        <v>44.82</v>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B2109" t="n">
+        <v>329.15</v>
+      </c>
+      <c r="C2109" t="n">
+        <v>108.48</v>
+      </c>
+      <c r="D2109" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E2109" t="n">
+        <v>438.9</v>
+      </c>
+      <c r="F2109" t="n">
+        <v>7.93</v>
+      </c>
+      <c r="G2109" t="n">
+        <v>58.36</v>
+      </c>
+      <c r="H2109" t="n">
+        <v>97.37</v>
+      </c>
+      <c r="I2109" t="n">
+        <v>155.73</v>
+      </c>
+      <c r="J2109" t="n">
+        <v>20.93</v>
+      </c>
+      <c r="K2109" t="n">
+        <v>24.83</v>
+      </c>
+      <c r="L2109" t="n">
+        <v>45.76</v>
+      </c>
+    </row>
+    <row r="2110">
+      <c r="A2110" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B2110" t="n">
+        <v>303.99</v>
+      </c>
+      <c r="C2110" t="n">
+        <v>118.78</v>
+      </c>
+      <c r="D2110" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="E2110" t="n">
+        <v>424.8</v>
+      </c>
+      <c r="F2110" t="n">
+        <v>7</v>
+      </c>
+      <c r="G2110" t="n">
+        <v>42.85</v>
+      </c>
+      <c r="H2110" t="n">
+        <v>87.12</v>
+      </c>
+      <c r="I2110" t="n">
+        <v>129.96</v>
+      </c>
+      <c r="J2110" t="n">
+        <v>20.06</v>
+      </c>
+      <c r="K2110" t="n">
+        <v>24.67</v>
+      </c>
+      <c r="L2110" t="n">
+        <v>44.73</v>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B2111" t="n">
+        <v>320.34</v>
+      </c>
+      <c r="C2111" t="n">
+        <v>125.1</v>
+      </c>
+      <c r="D2111" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="E2111" t="n">
+        <v>447.52</v>
+      </c>
+      <c r="F2111" t="n">
+        <v>7.82</v>
+      </c>
+      <c r="G2111" t="n">
+        <v>49.12</v>
+      </c>
+      <c r="H2111" t="n">
+        <v>84.41</v>
+      </c>
+      <c r="I2111" t="n">
+        <v>133.53</v>
+      </c>
+      <c r="J2111" t="n">
+        <v>19.33</v>
+      </c>
+      <c r="K2111" t="n">
+        <v>24.52</v>
+      </c>
+      <c r="L2111" t="n">
+        <v>43.85</v>
+      </c>
+    </row>
+    <row r="2112">
+      <c r="A2112" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B2112" t="n">
+        <v>376.05</v>
+      </c>
+      <c r="C2112" t="n">
+        <v>146.48</v>
+      </c>
+      <c r="D2112" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="E2112" t="n">
+        <v>524.01</v>
+      </c>
+      <c r="F2112" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="G2112" t="n">
+        <v>64.26000000000001</v>
+      </c>
+      <c r="H2112" t="n">
+        <v>112.57</v>
+      </c>
+      <c r="I2112" t="n">
+        <v>176.83</v>
+      </c>
+      <c r="J2112" t="n">
+        <v>28.41</v>
+      </c>
+      <c r="K2112" t="n">
+        <v>28.52</v>
+      </c>
+      <c r="L2112" t="n">
+        <v>56.93</v>
+      </c>
+    </row>
+    <row r="2113">
+      <c r="A2113" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B2113" t="n">
+        <v>398.11</v>
+      </c>
+      <c r="C2113" t="n">
+        <v>141.38</v>
+      </c>
+      <c r="D2113" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E2113" t="n">
+        <v>540.54</v>
+      </c>
+      <c r="F2113" t="n">
+        <v>9.74</v>
+      </c>
+      <c r="G2113" t="n">
+        <v>69.23</v>
+      </c>
+      <c r="H2113" t="n">
+        <v>132.41</v>
+      </c>
+      <c r="I2113" t="n">
+        <v>201.64</v>
+      </c>
+      <c r="J2113" t="n">
+        <v>31.93</v>
+      </c>
+      <c r="K2113" t="n">
+        <v>30.87</v>
+      </c>
+      <c r="L2113" t="n">
+        <v>62.8</v>
+      </c>
+    </row>
+    <row r="2114">
+      <c r="A2114" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B2114" t="n">
+        <v>406.31</v>
+      </c>
+      <c r="C2114" t="n">
+        <v>134.74</v>
+      </c>
+      <c r="D2114" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="E2114" t="n">
+        <v>542.22</v>
+      </c>
+      <c r="F2114" t="n">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="G2114" t="n">
+        <v>69.83</v>
+      </c>
+      <c r="H2114" t="n">
+        <v>144.67</v>
+      </c>
+      <c r="I2114" t="n">
+        <v>214.51</v>
+      </c>
+      <c r="J2114" t="n">
+        <v>34.12</v>
+      </c>
+      <c r="K2114" t="n">
+        <v>33.94</v>
+      </c>
+      <c r="L2114" t="n">
+        <v>68.05</v>
+      </c>
+    </row>
+    <row r="2115">
+      <c r="A2115" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B2115" t="n">
+        <v>408.77</v>
+      </c>
+      <c r="C2115" t="n">
+        <v>146.32</v>
+      </c>
+      <c r="D2115" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E2115" t="n">
+        <v>556.05</v>
+      </c>
+      <c r="F2115" t="n">
+        <v>9.84</v>
+      </c>
+      <c r="G2115" t="n">
+        <v>75.23999999999999</v>
+      </c>
+      <c r="H2115" t="n">
+        <v>162.05</v>
+      </c>
+      <c r="I2115" t="n">
+        <v>237.29</v>
+      </c>
+      <c r="J2115" t="n">
+        <v>32.19</v>
+      </c>
+      <c r="K2115" t="n">
+        <v>34.75</v>
+      </c>
+      <c r="L2115" t="n">
+        <v>66.93000000000001</v>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B2116" t="n">
+        <v>399.95</v>
+      </c>
+      <c r="C2116" t="n">
+        <v>146.11</v>
+      </c>
+      <c r="D2116" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="E2116" t="n">
+        <v>548.08</v>
+      </c>
+      <c r="F2116" t="n">
+        <v>9.01</v>
+      </c>
+      <c r="G2116" t="n">
+        <v>72.90000000000001</v>
+      </c>
+      <c r="H2116" t="n">
+        <v>171.02</v>
+      </c>
+      <c r="I2116" t="n">
+        <v>243.92</v>
+      </c>
+      <c r="J2116" t="n">
+        <v>31.65</v>
+      </c>
+      <c r="K2116" t="n">
+        <v>36.35</v>
+      </c>
+      <c r="L2116" t="n">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2117">
+      <c r="A2117" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B2117" t="n">
+        <v>374.11</v>
+      </c>
+      <c r="C2117" t="n">
+        <v>140.76</v>
+      </c>
+      <c r="D2117" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="E2117" t="n">
+        <v>516.85</v>
+      </c>
+      <c r="F2117" t="n">
+        <v>7.92</v>
+      </c>
+      <c r="G2117" t="n">
+        <v>69.52</v>
+      </c>
+      <c r="H2117" t="n">
+        <v>168.7</v>
+      </c>
+      <c r="I2117" t="n">
+        <v>238.22</v>
+      </c>
+      <c r="J2117" t="n">
+        <v>29.29</v>
+      </c>
+      <c r="K2117" t="n">
+        <v>35.46</v>
+      </c>
+      <c r="L2117" t="n">
+        <v>64.73999999999999</v>
+      </c>
+    </row>
+    <row r="2118">
+      <c r="A2118" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B2118" t="n">
+        <v>376.72</v>
+      </c>
+      <c r="C2118" t="n">
+        <v>136.52</v>
+      </c>
+      <c r="D2118" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="E2118" t="n">
+        <v>515.4400000000001</v>
+      </c>
+      <c r="F2118" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="G2118" t="n">
+        <v>66.27</v>
+      </c>
+      <c r="H2118" t="n">
+        <v>155.19</v>
+      </c>
+      <c r="I2118" t="n">
+        <v>221.46</v>
+      </c>
+      <c r="J2118" t="n">
+        <v>26.15</v>
+      </c>
+      <c r="K2118" t="n">
+        <v>34.33</v>
+      </c>
+      <c r="L2118" t="n">
+        <v>60.47</v>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B2119" t="n">
+        <v>433.55</v>
+      </c>
+      <c r="C2119" t="n">
+        <v>149.8</v>
+      </c>
+      <c r="D2119" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="E2119" t="n">
+        <v>585.64</v>
+      </c>
+      <c r="F2119" t="n">
+        <v>9.31</v>
+      </c>
+      <c r="G2119" t="n">
+        <v>71.59999999999999</v>
+      </c>
+      <c r="H2119" t="n">
+        <v>158.8</v>
+      </c>
+      <c r="I2119" t="n">
+        <v>230.4</v>
+      </c>
+      <c r="J2119" t="n">
+        <v>31.54</v>
+      </c>
+      <c r="K2119" t="n">
+        <v>34.37</v>
+      </c>
+      <c r="L2119" t="n">
+        <v>65.91</v>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B2120" t="n">
+        <v>427.41</v>
+      </c>
+      <c r="C2120" t="n">
+        <v>146.47</v>
+      </c>
+      <c r="D2120" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="E2120" t="n">
+        <v>576.11</v>
+      </c>
+      <c r="F2120" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="G2120" t="n">
+        <v>75.38</v>
+      </c>
+      <c r="H2120" t="n">
+        <v>149.85</v>
+      </c>
+      <c r="I2120" t="n">
+        <v>225.24</v>
+      </c>
+      <c r="J2120" t="n">
+        <v>30.8</v>
+      </c>
+      <c r="K2120" t="n">
+        <v>34.83</v>
+      </c>
+      <c r="L2120" t="n">
+        <v>65.64</v>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B2121" t="n">
+        <v>380.26</v>
+      </c>
+      <c r="C2121" t="n">
+        <v>118.13</v>
+      </c>
+      <c r="D2121" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="E2121" t="n">
+        <v>500.06</v>
+      </c>
+      <c r="F2121" t="n">
+        <v>10.27</v>
+      </c>
+      <c r="G2121" t="n">
+        <v>76.37</v>
+      </c>
+      <c r="H2121" t="n">
+        <v>147.35</v>
+      </c>
+      <c r="I2121" t="n">
+        <v>223.71</v>
+      </c>
+      <c r="J2121" t="n">
+        <v>31.03</v>
+      </c>
+      <c r="K2121" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="L2121" t="n">
+        <v>66.63</v>
+      </c>
+    </row>
+    <row r="2122">
+      <c r="A2122" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B2122" t="n">
+        <v>421</v>
+      </c>
+      <c r="C2122" t="n">
+        <v>134.69</v>
+      </c>
+      <c r="D2122" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="E2122" t="n">
+        <v>557.91</v>
+      </c>
+      <c r="F2122" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="G2122" t="n">
+        <v>80.11</v>
+      </c>
+      <c r="H2122" t="n">
+        <v>153.78</v>
+      </c>
+      <c r="I2122" t="n">
+        <v>233.89</v>
+      </c>
+      <c r="J2122" t="n">
+        <v>33.42</v>
+      </c>
+      <c r="K2122" t="n">
+        <v>36.37</v>
+      </c>
+      <c r="L2122" t="n">
+        <v>69.8</v>
+      </c>
+    </row>
+    <row r="2123">
+      <c r="A2123" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B2123" t="n">
+        <v>412.99</v>
+      </c>
+      <c r="C2123" t="n">
+        <v>124.03</v>
+      </c>
+      <c r="D2123" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="E2123" t="n">
+        <v>538.95</v>
+      </c>
+      <c r="F2123" t="n">
+        <v>10.52</v>
+      </c>
+      <c r="G2123" t="n">
+        <v>79.02</v>
+      </c>
+      <c r="H2123" t="n">
+        <v>168.69</v>
+      </c>
+      <c r="I2123" t="n">
+        <v>247.71</v>
+      </c>
+      <c r="J2123" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="K2123" t="n">
+        <v>37.76</v>
+      </c>
+      <c r="L2123" t="n">
+        <v>75.66</v>
+      </c>
+    </row>
+    <row r="2124">
+      <c r="A2124" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B2124" t="n">
+        <v>416.28</v>
+      </c>
+      <c r="C2124" t="n">
+        <v>106.09</v>
+      </c>
+      <c r="D2124" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="E2124" t="n">
+        <v>524.65</v>
+      </c>
+      <c r="F2124" t="n">
+        <v>10.79</v>
+      </c>
+      <c r="G2124" t="n">
+        <v>76.59</v>
+      </c>
+      <c r="H2124" t="n">
+        <v>175.92</v>
+      </c>
+      <c r="I2124" t="n">
+        <v>252.51</v>
+      </c>
+      <c r="J2124" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="K2124" t="n">
+        <v>39.09</v>
+      </c>
+      <c r="L2124" t="n">
+        <v>75.79000000000001</v>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B2125" t="n">
+        <v>403.85</v>
+      </c>
+      <c r="C2125" t="n">
+        <v>98</v>
+      </c>
+      <c r="D2125" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E2125" t="n">
+        <v>503.89</v>
+      </c>
+      <c r="F2125" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="G2125" t="n">
+        <v>77.09999999999999</v>
+      </c>
+      <c r="H2125" t="n">
+        <v>168.41</v>
+      </c>
+      <c r="I2125" t="n">
+        <v>245.51</v>
+      </c>
+      <c r="J2125" t="n">
+        <v>35.17</v>
+      </c>
+      <c r="K2125" t="n">
+        <v>37.09</v>
+      </c>
+      <c r="L2125" t="n">
+        <v>72.26000000000001</v>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B2126" t="n">
+        <v>459.62</v>
+      </c>
+      <c r="C2126" t="n">
+        <v>132.2</v>
+      </c>
+      <c r="D2126" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="E2126" t="n">
+        <v>594.14</v>
+      </c>
+      <c r="F2126" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="G2126" t="n">
+        <v>79.64</v>
+      </c>
+      <c r="H2126" t="n">
+        <v>194.06</v>
+      </c>
+      <c r="I2126" t="n">
+        <v>273.69</v>
+      </c>
+      <c r="J2126" t="n">
+        <v>38.96</v>
+      </c>
+      <c r="K2126" t="n">
+        <v>38.22</v>
+      </c>
+      <c r="L2126" t="n">
+        <v>77.18000000000001</v>
+      </c>
+    </row>
+    <row r="2127">
+      <c r="A2127" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="J2127" t="n">
+        <v>22.22</v>
+      </c>
+      <c r="K2127" t="n">
+        <v>19.52</v>
+      </c>
+      <c r="L2127" t="n">
+        <v>41.73</v>
       </c>
     </row>
   </sheetData>
@@ -86738,7 +87472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88241,6 +88975,28 @@
         <v>948</v>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B70" t="n">
+        <v>25817</v>
+      </c>
+      <c r="C70" t="n">
+        <v>14568</v>
+      </c>
+      <c r="D70" t="n">
+        <v>11250</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Boletín%20Estadístico_sep26_ingles.pdf</t>
+        </is>
+      </c>
+      <c r="F70" t="n">
+        <v>960</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
